--- a/output/test-config/level-tags/LevelTagCfg.xlsx
+++ b/output/test-config/level-tags/LevelTagCfg.xlsx
@@ -513,46 +513,11 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="n">
         <v>1</v>
@@ -566,8 +531,6 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -582,8 +545,6 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -598,8 +559,6 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -614,8 +573,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -630,8 +587,6 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -646,8 +601,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -662,8 +615,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -678,8 +629,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -694,8 +643,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -710,8 +657,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -726,8 +671,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -742,8 +685,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -758,8 +699,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -774,8 +713,6 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -790,8 +727,6 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -806,8 +741,6 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -822,8 +755,6 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -838,8 +769,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -854,8 +783,6 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -870,8 +797,6 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -886,8 +811,6 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -902,8 +825,6 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -918,8 +839,6 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -934,8 +853,6 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -950,8 +867,6 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -966,8 +881,6 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -982,8 +895,6 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -998,8 +909,6 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1014,8 +923,6 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1030,8 +937,6 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1046,8 +951,6 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1062,8 +965,6 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1078,8 +979,6 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1094,8 +993,6 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1110,8 +1007,6 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1126,8 +1021,6 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1142,8 +1035,6 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1158,8 +1049,6 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1174,8 +1063,6 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1190,8 +1077,6 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1206,8 +1091,6 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1222,8 +1105,6 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1238,8 +1119,6 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1254,8 +1133,6 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1270,8 +1147,6 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1286,8 +1161,6 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1302,8 +1175,6 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1318,8 +1189,6 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1334,8 +1203,6 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1350,8 +1217,6 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1366,8 +1231,6 @@
       <c r="D59" t="n">
         <v>2</v>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1382,8 +1245,6 @@
       <c r="D60" t="n">
         <v>2</v>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1398,8 +1259,6 @@
       <c r="D61" t="n">
         <v>2</v>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1414,8 +1273,6 @@
       <c r="D62" t="n">
         <v>2</v>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1430,8 +1287,6 @@
       <c r="D63" t="n">
         <v>2</v>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1446,8 +1301,6 @@
       <c r="D64" t="n">
         <v>2</v>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1462,8 +1315,6 @@
       <c r="D65" t="n">
         <v>2</v>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1478,8 +1329,6 @@
       <c r="D66" t="n">
         <v>2</v>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1494,8 +1343,6 @@
       <c r="D67" t="n">
         <v>2</v>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1510,8 +1357,6 @@
       <c r="D68" t="n">
         <v>2</v>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1526,8 +1371,6 @@
       <c r="D69" t="n">
         <v>2</v>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1542,8 +1385,6 @@
       <c r="D70" t="n">
         <v>2</v>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1558,8 +1399,6 @@
       <c r="D71" t="n">
         <v>2</v>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1574,8 +1413,6 @@
       <c r="D72" t="n">
         <v>2</v>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1590,8 +1427,6 @@
       <c r="D73" t="n">
         <v>2</v>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1606,8 +1441,6 @@
       <c r="D74" t="n">
         <v>2</v>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1622,8 +1455,6 @@
       <c r="D75" t="n">
         <v>2</v>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1638,8 +1469,6 @@
       <c r="D76" t="n">
         <v>2</v>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1654,8 +1483,6 @@
       <c r="D77" t="n">
         <v>2</v>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1670,8 +1497,6 @@
       <c r="D78" t="n">
         <v>2</v>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1686,8 +1511,6 @@
       <c r="D79" t="n">
         <v>2</v>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1702,8 +1525,6 @@
       <c r="D80" t="n">
         <v>2</v>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1718,8 +1539,6 @@
       <c r="D81" t="n">
         <v>2</v>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1734,8 +1553,6 @@
       <c r="D82" t="n">
         <v>2</v>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1750,8 +1567,6 @@
       <c r="D83" t="n">
         <v>2</v>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1766,8 +1581,6 @@
       <c r="D84" t="n">
         <v>2</v>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1782,8 +1595,6 @@
       <c r="D85" t="n">
         <v>2</v>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1798,8 +1609,6 @@
       <c r="D86" t="n">
         <v>2</v>
       </c>
-      <c r="E86" t="inlineStr"/>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1814,8 +1623,6 @@
       <c r="D87" t="n">
         <v>2</v>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1830,8 +1637,6 @@
       <c r="D88" t="n">
         <v>2</v>
       </c>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1846,8 +1651,6 @@
       <c r="D89" t="n">
         <v>2</v>
       </c>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1862,8 +1665,6 @@
       <c r="D90" t="n">
         <v>2</v>
       </c>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1878,8 +1679,6 @@
       <c r="D91" t="n">
         <v>2</v>
       </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1894,8 +1693,6 @@
       <c r="D92" t="n">
         <v>2</v>
       </c>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1910,8 +1707,6 @@
       <c r="D93" t="n">
         <v>2</v>
       </c>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1926,8 +1721,6 @@
       <c r="D94" t="n">
         <v>2</v>
       </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1942,8 +1735,6 @@
       <c r="D95" t="n">
         <v>2</v>
       </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1958,8 +1749,6 @@
       <c r="D96" t="n">
         <v>2</v>
       </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1974,8 +1763,6 @@
       <c r="D97" t="n">
         <v>2</v>
       </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1990,8 +1777,6 @@
       <c r="D98" t="n">
         <v>2</v>
       </c>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2006,8 +1791,6 @@
       <c r="D99" t="n">
         <v>2</v>
       </c>
-      <c r="E99" t="inlineStr"/>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2022,8 +1805,6 @@
       <c r="D100" t="n">
         <v>2</v>
       </c>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2038,8 +1819,6 @@
       <c r="D101" t="n">
         <v>2</v>
       </c>
-      <c r="E101" t="inlineStr"/>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2054,8 +1833,6 @@
       <c r="D102" t="n">
         <v>2</v>
       </c>
-      <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2070,8 +1847,6 @@
       <c r="D103" t="n">
         <v>2</v>
       </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2086,8 +1861,6 @@
       <c r="D104" t="n">
         <v>2</v>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2102,8 +1875,6 @@
       <c r="D105" t="n">
         <v>2</v>
       </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2118,8 +1889,6 @@
       <c r="D106" t="n">
         <v>2</v>
       </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2134,8 +1903,6 @@
       <c r="D107" t="n">
         <v>2</v>
       </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2150,8 +1917,11 @@
       <c r="D108" t="n">
         <v>2</v>
       </c>
-      <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2166,8 +1936,6 @@
       <c r="D109" t="n">
         <v>3</v>
       </c>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2182,8 +1950,6 @@
       <c r="D110" t="n">
         <v>3</v>
       </c>
-      <c r="E110" t="inlineStr"/>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2198,8 +1964,6 @@
       <c r="D111" t="n">
         <v>3</v>
       </c>
-      <c r="E111" t="inlineStr"/>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2214,8 +1978,6 @@
       <c r="D112" t="n">
         <v>3</v>
       </c>
-      <c r="E112" t="inlineStr"/>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2230,8 +1992,6 @@
       <c r="D113" t="n">
         <v>3</v>
       </c>
-      <c r="E113" t="inlineStr"/>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2246,8 +2006,6 @@
       <c r="D114" t="n">
         <v>3</v>
       </c>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2262,8 +2020,6 @@
       <c r="D115" t="n">
         <v>3</v>
       </c>
-      <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2278,8 +2034,6 @@
       <c r="D116" t="n">
         <v>3</v>
       </c>
-      <c r="E116" t="inlineStr"/>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2294,8 +2048,6 @@
       <c r="D117" t="n">
         <v>3</v>
       </c>
-      <c r="E117" t="inlineStr"/>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2310,8 +2062,6 @@
       <c r="D118" t="n">
         <v>3</v>
       </c>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2326,8 +2076,6 @@
       <c r="D119" t="n">
         <v>3</v>
       </c>
-      <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2342,8 +2090,6 @@
       <c r="D120" t="n">
         <v>3</v>
       </c>
-      <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2358,8 +2104,6 @@
       <c r="D121" t="n">
         <v>3</v>
       </c>
-      <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2374,8 +2118,6 @@
       <c r="D122" t="n">
         <v>3</v>
       </c>
-      <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2390,8 +2132,6 @@
       <c r="D123" t="n">
         <v>3</v>
       </c>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2406,8 +2146,6 @@
       <c r="D124" t="n">
         <v>3</v>
       </c>
-      <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2422,8 +2160,6 @@
       <c r="D125" t="n">
         <v>3</v>
       </c>
-      <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2438,8 +2174,6 @@
       <c r="D126" t="n">
         <v>3</v>
       </c>
-      <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2454,8 +2188,6 @@
       <c r="D127" t="n">
         <v>3</v>
       </c>
-      <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2470,8 +2202,6 @@
       <c r="D128" t="n">
         <v>3</v>
       </c>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2486,8 +2216,6 @@
       <c r="D129" t="n">
         <v>3</v>
       </c>
-      <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2502,8 +2230,6 @@
       <c r="D130" t="n">
         <v>3</v>
       </c>
-      <c r="E130" t="inlineStr"/>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2518,8 +2244,6 @@
       <c r="D131" t="n">
         <v>3</v>
       </c>
-      <c r="E131" t="inlineStr"/>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2534,8 +2258,6 @@
       <c r="D132" t="n">
         <v>3</v>
       </c>
-      <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2550,8 +2272,6 @@
       <c r="D133" t="n">
         <v>3</v>
       </c>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2566,8 +2286,6 @@
       <c r="D134" t="n">
         <v>3</v>
       </c>
-      <c r="E134" t="inlineStr"/>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2582,8 +2300,6 @@
       <c r="D135" t="n">
         <v>3</v>
       </c>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2598,8 +2314,6 @@
       <c r="D136" t="n">
         <v>3</v>
       </c>
-      <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2614,8 +2328,6 @@
       <c r="D137" t="n">
         <v>3</v>
       </c>
-      <c r="E137" t="inlineStr"/>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2630,8 +2342,6 @@
       <c r="D138" t="n">
         <v>3</v>
       </c>
-      <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2646,8 +2356,6 @@
       <c r="D139" t="n">
         <v>3</v>
       </c>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2662,8 +2370,6 @@
       <c r="D140" t="n">
         <v>3</v>
       </c>
-      <c r="E140" t="inlineStr"/>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2678,8 +2384,6 @@
       <c r="D141" t="n">
         <v>3</v>
       </c>
-      <c r="E141" t="inlineStr"/>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2694,8 +2398,6 @@
       <c r="D142" t="n">
         <v>3</v>
       </c>
-      <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2710,8 +2412,6 @@
       <c r="D143" t="n">
         <v>3</v>
       </c>
-      <c r="E143" t="inlineStr"/>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2726,8 +2426,6 @@
       <c r="D144" t="n">
         <v>3</v>
       </c>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2742,8 +2440,6 @@
       <c r="D145" t="n">
         <v>3</v>
       </c>
-      <c r="E145" t="inlineStr"/>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2758,8 +2454,6 @@
       <c r="D146" t="n">
         <v>3</v>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2774,8 +2468,6 @@
       <c r="D147" t="n">
         <v>3</v>
       </c>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2790,8 +2482,6 @@
       <c r="D148" t="n">
         <v>3</v>
       </c>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2806,8 +2496,6 @@
       <c r="D149" t="n">
         <v>3</v>
       </c>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2822,8 +2510,6 @@
       <c r="D150" t="n">
         <v>3</v>
       </c>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2838,8 +2524,6 @@
       <c r="D151" t="n">
         <v>3</v>
       </c>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2854,8 +2538,6 @@
       <c r="D152" t="n">
         <v>3</v>
       </c>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2870,8 +2552,6 @@
       <c r="D153" t="n">
         <v>3</v>
       </c>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2886,8 +2566,6 @@
       <c r="D154" t="n">
         <v>3</v>
       </c>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2902,8 +2580,6 @@
       <c r="D155" t="n">
         <v>3</v>
       </c>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2918,8 +2594,6 @@
       <c r="D156" t="n">
         <v>3</v>
       </c>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2934,8 +2608,6 @@
       <c r="D157" t="n">
         <v>3</v>
       </c>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2950,8 +2622,6 @@
       <c r="D158" t="n">
         <v>3</v>
       </c>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2966,8 +2636,6 @@
       <c r="D159" t="n">
         <v>4</v>
       </c>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2982,8 +2650,6 @@
       <c r="D160" t="n">
         <v>4</v>
       </c>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2998,8 +2664,6 @@
       <c r="D161" t="n">
         <v>4</v>
       </c>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3014,8 +2678,6 @@
       <c r="D162" t="n">
         <v>4</v>
       </c>
-      <c r="E162" t="inlineStr"/>
-      <c r="F162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3030,8 +2692,6 @@
       <c r="D163" t="n">
         <v>4</v>
       </c>
-      <c r="E163" t="inlineStr"/>
-      <c r="F163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3046,8 +2706,6 @@
       <c r="D164" t="n">
         <v>4</v>
       </c>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3062,8 +2720,6 @@
       <c r="D165" t="n">
         <v>4</v>
       </c>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3078,8 +2734,6 @@
       <c r="D166" t="n">
         <v>4</v>
       </c>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3094,8 +2748,6 @@
       <c r="D167" t="n">
         <v>4</v>
       </c>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3110,8 +2762,6 @@
       <c r="D168" t="n">
         <v>4</v>
       </c>
-      <c r="E168" t="inlineStr"/>
-      <c r="F168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3126,8 +2776,6 @@
       <c r="D169" t="n">
         <v>4</v>
       </c>
-      <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -3142,8 +2790,6 @@
       <c r="D170" t="n">
         <v>4</v>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -3158,8 +2804,6 @@
       <c r="D171" t="n">
         <v>4</v>
       </c>
-      <c r="E171" t="inlineStr"/>
-      <c r="F171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -3174,8 +2818,6 @@
       <c r="D172" t="n">
         <v>4</v>
       </c>
-      <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -3190,8 +2832,6 @@
       <c r="D173" t="n">
         <v>4</v>
       </c>
-      <c r="E173" t="inlineStr"/>
-      <c r="F173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -3206,8 +2846,6 @@
       <c r="D174" t="n">
         <v>4</v>
       </c>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -3222,8 +2860,6 @@
       <c r="D175" t="n">
         <v>4</v>
       </c>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -3238,8 +2874,6 @@
       <c r="D176" t="n">
         <v>4</v>
       </c>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -3254,8 +2888,6 @@
       <c r="D177" t="n">
         <v>4</v>
       </c>
-      <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -3270,8 +2902,6 @@
       <c r="D178" t="n">
         <v>4</v>
       </c>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -3286,8 +2916,6 @@
       <c r="D179" t="n">
         <v>4</v>
       </c>
-      <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -3302,8 +2930,6 @@
       <c r="D180" t="n">
         <v>4</v>
       </c>
-      <c r="E180" t="inlineStr"/>
-      <c r="F180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -3318,8 +2944,6 @@
       <c r="D181" t="n">
         <v>4</v>
       </c>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -3334,8 +2958,6 @@
       <c r="D182" t="n">
         <v>4</v>
       </c>
-      <c r="E182" t="inlineStr"/>
-      <c r="F182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -3350,8 +2972,6 @@
       <c r="D183" t="n">
         <v>4</v>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -3366,8 +2986,6 @@
       <c r="D184" t="n">
         <v>4</v>
       </c>
-      <c r="E184" t="inlineStr"/>
-      <c r="F184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3382,8 +3000,6 @@
       <c r="D185" t="n">
         <v>4</v>
       </c>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3398,8 +3014,6 @@
       <c r="D186" t="n">
         <v>4</v>
       </c>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3414,8 +3028,6 @@
       <c r="D187" t="n">
         <v>4</v>
       </c>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3430,8 +3042,6 @@
       <c r="D188" t="n">
         <v>4</v>
       </c>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3446,8 +3056,6 @@
       <c r="D189" t="n">
         <v>4</v>
       </c>
-      <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3462,8 +3070,6 @@
       <c r="D190" t="n">
         <v>4</v>
       </c>
-      <c r="E190" t="inlineStr"/>
-      <c r="F190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3478,8 +3084,6 @@
       <c r="D191" t="n">
         <v>4</v>
       </c>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3494,8 +3098,6 @@
       <c r="D192" t="n">
         <v>4</v>
       </c>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3510,8 +3112,6 @@
       <c r="D193" t="n">
         <v>4</v>
       </c>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3526,8 +3126,6 @@
       <c r="D194" t="n">
         <v>4</v>
       </c>
-      <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3542,8 +3140,6 @@
       <c r="D195" t="n">
         <v>4</v>
       </c>
-      <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3558,8 +3154,6 @@
       <c r="D196" t="n">
         <v>4</v>
       </c>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3574,8 +3168,6 @@
       <c r="D197" t="n">
         <v>4</v>
       </c>
-      <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3590,8 +3182,6 @@
       <c r="D198" t="n">
         <v>4</v>
       </c>
-      <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3606,8 +3196,6 @@
       <c r="D199" t="n">
         <v>4</v>
       </c>
-      <c r="E199" t="inlineStr"/>
-      <c r="F199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3622,8 +3210,6 @@
       <c r="D200" t="n">
         <v>4</v>
       </c>
-      <c r="E200" t="inlineStr"/>
-      <c r="F200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3638,8 +3224,6 @@
       <c r="D201" t="n">
         <v>4</v>
       </c>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3654,8 +3238,6 @@
       <c r="D202" t="n">
         <v>4</v>
       </c>
-      <c r="E202" t="inlineStr"/>
-      <c r="F202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3670,8 +3252,6 @@
       <c r="D203" t="n">
         <v>4</v>
       </c>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3686,8 +3266,6 @@
       <c r="D204" t="n">
         <v>4</v>
       </c>
-      <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3702,8 +3280,6 @@
       <c r="D205" t="n">
         <v>4</v>
       </c>
-      <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3718,8 +3294,6 @@
       <c r="D206" t="n">
         <v>4</v>
       </c>
-      <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3734,8 +3308,6 @@
       <c r="D207" t="n">
         <v>4</v>
       </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3750,8 +3322,11 @@
       <c r="D208" t="n">
         <v>4</v>
       </c>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3766,8 +3341,6 @@
       <c r="D209" t="n">
         <v>5</v>
       </c>
-      <c r="E209" t="inlineStr"/>
-      <c r="F209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3782,8 +3355,6 @@
       <c r="D210" t="n">
         <v>5</v>
       </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3798,8 +3369,6 @@
       <c r="D211" t="n">
         <v>5</v>
       </c>
-      <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3814,8 +3383,6 @@
       <c r="D212" t="n">
         <v>5</v>
       </c>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3830,8 +3397,6 @@
       <c r="D213" t="n">
         <v>5</v>
       </c>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3846,8 +3411,6 @@
       <c r="D214" t="n">
         <v>5</v>
       </c>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3862,8 +3425,6 @@
       <c r="D215" t="n">
         <v>5</v>
       </c>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3878,8 +3439,6 @@
       <c r="D216" t="n">
         <v>5</v>
       </c>
-      <c r="E216" t="inlineStr"/>
-      <c r="F216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3894,8 +3453,6 @@
       <c r="D217" t="n">
         <v>5</v>
       </c>
-      <c r="E217" t="inlineStr"/>
-      <c r="F217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3910,8 +3467,6 @@
       <c r="D218" t="n">
         <v>5</v>
       </c>
-      <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3926,8 +3481,6 @@
       <c r="D219" t="n">
         <v>5</v>
       </c>
-      <c r="E219" t="inlineStr"/>
-      <c r="F219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3942,8 +3495,6 @@
       <c r="D220" t="n">
         <v>5</v>
       </c>
-      <c r="E220" t="inlineStr"/>
-      <c r="F220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3958,8 +3509,6 @@
       <c r="D221" t="n">
         <v>5</v>
       </c>
-      <c r="E221" t="inlineStr"/>
-      <c r="F221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3974,8 +3523,6 @@
       <c r="D222" t="n">
         <v>5</v>
       </c>
-      <c r="E222" t="inlineStr"/>
-      <c r="F222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3990,8 +3537,6 @@
       <c r="D223" t="n">
         <v>5</v>
       </c>
-      <c r="E223" t="inlineStr"/>
-      <c r="F223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -4006,8 +3551,6 @@
       <c r="D224" t="n">
         <v>5</v>
       </c>
-      <c r="E224" t="inlineStr"/>
-      <c r="F224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -4022,8 +3565,6 @@
       <c r="D225" t="n">
         <v>5</v>
       </c>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -4038,8 +3579,6 @@
       <c r="D226" t="n">
         <v>5</v>
       </c>
-      <c r="E226" t="inlineStr"/>
-      <c r="F226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -4054,8 +3593,6 @@
       <c r="D227" t="n">
         <v>5</v>
       </c>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -4070,8 +3607,6 @@
       <c r="D228" t="n">
         <v>5</v>
       </c>
-      <c r="E228" t="inlineStr"/>
-      <c r="F228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -4086,8 +3621,6 @@
       <c r="D229" t="n">
         <v>5</v>
       </c>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -4102,8 +3635,6 @@
       <c r="D230" t="n">
         <v>5</v>
       </c>
-      <c r="E230" t="inlineStr"/>
-      <c r="F230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -4118,8 +3649,6 @@
       <c r="D231" t="n">
         <v>5</v>
       </c>
-      <c r="E231" t="inlineStr"/>
-      <c r="F231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -4134,8 +3663,6 @@
       <c r="D232" t="n">
         <v>5</v>
       </c>
-      <c r="E232" t="inlineStr"/>
-      <c r="F232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -4150,8 +3677,6 @@
       <c r="D233" t="n">
         <v>5</v>
       </c>
-      <c r="E233" t="inlineStr"/>
-      <c r="F233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -4166,8 +3691,6 @@
       <c r="D234" t="n">
         <v>5</v>
       </c>
-      <c r="E234" t="inlineStr"/>
-      <c r="F234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -4182,8 +3705,6 @@
       <c r="D235" t="n">
         <v>5</v>
       </c>
-      <c r="E235" t="inlineStr"/>
-      <c r="F235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -4198,8 +3719,6 @@
       <c r="D236" t="n">
         <v>5</v>
       </c>
-      <c r="E236" t="inlineStr"/>
-      <c r="F236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -4214,8 +3733,6 @@
       <c r="D237" t="n">
         <v>5</v>
       </c>
-      <c r="E237" t="inlineStr"/>
-      <c r="F237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -4230,8 +3747,6 @@
       <c r="D238" t="n">
         <v>5</v>
       </c>
-      <c r="E238" t="inlineStr"/>
-      <c r="F238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -4246,8 +3761,6 @@
       <c r="D239" t="n">
         <v>5</v>
       </c>
-      <c r="E239" t="inlineStr"/>
-      <c r="F239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -4262,8 +3775,6 @@
       <c r="D240" t="n">
         <v>5</v>
       </c>
-      <c r="E240" t="inlineStr"/>
-      <c r="F240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -4278,8 +3789,6 @@
       <c r="D241" t="n">
         <v>5</v>
       </c>
-      <c r="E241" t="inlineStr"/>
-      <c r="F241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -4294,8 +3803,6 @@
       <c r="D242" t="n">
         <v>5</v>
       </c>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -4310,8 +3817,6 @@
       <c r="D243" t="n">
         <v>5</v>
       </c>
-      <c r="E243" t="inlineStr"/>
-      <c r="F243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -4326,8 +3831,6 @@
       <c r="D244" t="n">
         <v>5</v>
       </c>
-      <c r="E244" t="inlineStr"/>
-      <c r="F244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -4342,8 +3845,6 @@
       <c r="D245" t="n">
         <v>5</v>
       </c>
-      <c r="E245" t="inlineStr"/>
-      <c r="F245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -4358,8 +3859,6 @@
       <c r="D246" t="n">
         <v>5</v>
       </c>
-      <c r="E246" t="inlineStr"/>
-      <c r="F246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -4374,8 +3873,6 @@
       <c r="D247" t="n">
         <v>5</v>
       </c>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -4390,8 +3887,6 @@
       <c r="D248" t="n">
         <v>5</v>
       </c>
-      <c r="E248" t="inlineStr"/>
-      <c r="F248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -4406,8 +3901,6 @@
       <c r="D249" t="n">
         <v>5</v>
       </c>
-      <c r="E249" t="inlineStr"/>
-      <c r="F249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -4422,8 +3915,6 @@
       <c r="D250" t="n">
         <v>5</v>
       </c>
-      <c r="E250" t="inlineStr"/>
-      <c r="F250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -4438,8 +3929,6 @@
       <c r="D251" t="n">
         <v>5</v>
       </c>
-      <c r="E251" t="inlineStr"/>
-      <c r="F251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -4454,8 +3943,6 @@
       <c r="D252" t="n">
         <v>5</v>
       </c>
-      <c r="E252" t="inlineStr"/>
-      <c r="F252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -4470,8 +3957,6 @@
       <c r="D253" t="n">
         <v>5</v>
       </c>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -4486,8 +3971,6 @@
       <c r="D254" t="n">
         <v>5</v>
       </c>
-      <c r="E254" t="inlineStr"/>
-      <c r="F254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -4502,8 +3985,6 @@
       <c r="D255" t="n">
         <v>5</v>
       </c>
-      <c r="E255" t="inlineStr"/>
-      <c r="F255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -4518,8 +3999,6 @@
       <c r="D256" t="n">
         <v>5</v>
       </c>
-      <c r="E256" t="inlineStr"/>
-      <c r="F256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4534,8 +4013,6 @@
       <c r="D257" t="n">
         <v>5</v>
       </c>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4550,8 +4027,11 @@
       <c r="D258" t="n">
         <v>5</v>
       </c>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>extreme_keeper</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -4566,8 +4046,6 @@
       <c r="D259" t="n">
         <v>6</v>
       </c>
-      <c r="E259" t="inlineStr"/>
-      <c r="F259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4582,8 +4060,6 @@
       <c r="D260" t="n">
         <v>6</v>
       </c>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4598,8 +4074,6 @@
       <c r="D261" t="n">
         <v>6</v>
       </c>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4614,8 +4088,6 @@
       <c r="D262" t="n">
         <v>6</v>
       </c>
-      <c r="E262" t="inlineStr"/>
-      <c r="F262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4630,8 +4102,6 @@
       <c r="D263" t="n">
         <v>6</v>
       </c>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4646,8 +4116,6 @@
       <c r="D264" t="n">
         <v>6</v>
       </c>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4662,8 +4130,6 @@
       <c r="D265" t="n">
         <v>6</v>
       </c>
-      <c r="E265" t="inlineStr"/>
-      <c r="F265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4678,8 +4144,6 @@
       <c r="D266" t="n">
         <v>6</v>
       </c>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4694,8 +4158,6 @@
       <c r="D267" t="n">
         <v>6</v>
       </c>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4710,8 +4172,6 @@
       <c r="D268" t="n">
         <v>6</v>
       </c>
-      <c r="E268" t="inlineStr"/>
-      <c r="F268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4726,8 +4186,6 @@
       <c r="D269" t="n">
         <v>6</v>
       </c>
-      <c r="E269" t="inlineStr"/>
-      <c r="F269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4742,8 +4200,6 @@
       <c r="D270" t="n">
         <v>6</v>
       </c>
-      <c r="E270" t="inlineStr"/>
-      <c r="F270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4758,8 +4214,6 @@
       <c r="D271" t="n">
         <v>6</v>
       </c>
-      <c r="E271" t="inlineStr"/>
-      <c r="F271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4774,8 +4228,6 @@
       <c r="D272" t="n">
         <v>6</v>
       </c>
-      <c r="E272" t="inlineStr"/>
-      <c r="F272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4790,8 +4242,6 @@
       <c r="D273" t="n">
         <v>6</v>
       </c>
-      <c r="E273" t="inlineStr"/>
-      <c r="F273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4806,8 +4256,6 @@
       <c r="D274" t="n">
         <v>6</v>
       </c>
-      <c r="E274" t="inlineStr"/>
-      <c r="F274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4822,8 +4270,6 @@
       <c r="D275" t="n">
         <v>6</v>
       </c>
-      <c r="E275" t="inlineStr"/>
-      <c r="F275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4838,8 +4284,6 @@
       <c r="D276" t="n">
         <v>6</v>
       </c>
-      <c r="E276" t="inlineStr"/>
-      <c r="F276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4854,8 +4298,6 @@
       <c r="D277" t="n">
         <v>6</v>
       </c>
-      <c r="E277" t="inlineStr"/>
-      <c r="F277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4870,8 +4312,6 @@
       <c r="D278" t="n">
         <v>6</v>
       </c>
-      <c r="E278" t="inlineStr"/>
-      <c r="F278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4886,8 +4326,6 @@
       <c r="D279" t="n">
         <v>6</v>
       </c>
-      <c r="E279" t="inlineStr"/>
-      <c r="F279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4902,8 +4340,6 @@
       <c r="D280" t="n">
         <v>6</v>
       </c>
-      <c r="E280" t="inlineStr"/>
-      <c r="F280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4918,8 +4354,6 @@
       <c r="D281" t="n">
         <v>6</v>
       </c>
-      <c r="E281" t="inlineStr"/>
-      <c r="F281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4934,8 +4368,6 @@
       <c r="D282" t="n">
         <v>6</v>
       </c>
-      <c r="E282" t="inlineStr"/>
-      <c r="F282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4950,8 +4382,6 @@
       <c r="D283" t="n">
         <v>6</v>
       </c>
-      <c r="E283" t="inlineStr"/>
-      <c r="F283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -4966,8 +4396,6 @@
       <c r="D284" t="n">
         <v>6</v>
       </c>
-      <c r="E284" t="inlineStr"/>
-      <c r="F284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4982,8 +4410,6 @@
       <c r="D285" t="n">
         <v>6</v>
       </c>
-      <c r="E285" t="inlineStr"/>
-      <c r="F285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -4998,8 +4424,6 @@
       <c r="D286" t="n">
         <v>6</v>
       </c>
-      <c r="E286" t="inlineStr"/>
-      <c r="F286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -5014,8 +4438,6 @@
       <c r="D287" t="n">
         <v>6</v>
       </c>
-      <c r="E287" t="inlineStr"/>
-      <c r="F287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -5030,8 +4452,6 @@
       <c r="D288" t="n">
         <v>6</v>
       </c>
-      <c r="E288" t="inlineStr"/>
-      <c r="F288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -5046,8 +4466,6 @@
       <c r="D289" t="n">
         <v>6</v>
       </c>
-      <c r="E289" t="inlineStr"/>
-      <c r="F289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -5062,8 +4480,6 @@
       <c r="D290" t="n">
         <v>6</v>
       </c>
-      <c r="E290" t="inlineStr"/>
-      <c r="F290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -5078,8 +4494,6 @@
       <c r="D291" t="n">
         <v>6</v>
       </c>
-      <c r="E291" t="inlineStr"/>
-      <c r="F291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -5094,8 +4508,6 @@
       <c r="D292" t="n">
         <v>6</v>
       </c>
-      <c r="E292" t="inlineStr"/>
-      <c r="F292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -5110,8 +4522,6 @@
       <c r="D293" t="n">
         <v>6</v>
       </c>
-      <c r="E293" t="inlineStr"/>
-      <c r="F293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -5126,8 +4536,6 @@
       <c r="D294" t="n">
         <v>6</v>
       </c>
-      <c r="E294" t="inlineStr"/>
-      <c r="F294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -5142,8 +4550,6 @@
       <c r="D295" t="n">
         <v>6</v>
       </c>
-      <c r="E295" t="inlineStr"/>
-      <c r="F295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -5158,8 +4564,6 @@
       <c r="D296" t="n">
         <v>6</v>
       </c>
-      <c r="E296" t="inlineStr"/>
-      <c r="F296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -5174,8 +4578,6 @@
       <c r="D297" t="n">
         <v>6</v>
       </c>
-      <c r="E297" t="inlineStr"/>
-      <c r="F297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -5190,8 +4592,6 @@
       <c r="D298" t="n">
         <v>6</v>
       </c>
-      <c r="E298" t="inlineStr"/>
-      <c r="F298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -5206,8 +4606,6 @@
       <c r="D299" t="n">
         <v>6</v>
       </c>
-      <c r="E299" t="inlineStr"/>
-      <c r="F299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -5222,8 +4620,6 @@
       <c r="D300" t="n">
         <v>6</v>
       </c>
-      <c r="E300" t="inlineStr"/>
-      <c r="F300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -5238,8 +4634,6 @@
       <c r="D301" t="n">
         <v>6</v>
       </c>
-      <c r="E301" t="inlineStr"/>
-      <c r="F301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -5254,8 +4648,6 @@
       <c r="D302" t="n">
         <v>6</v>
       </c>
-      <c r="E302" t="inlineStr"/>
-      <c r="F302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -5270,8 +4662,6 @@
       <c r="D303" t="n">
         <v>6</v>
       </c>
-      <c r="E303" t="inlineStr"/>
-      <c r="F303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -5286,8 +4676,6 @@
       <c r="D304" t="n">
         <v>6</v>
       </c>
-      <c r="E304" t="inlineStr"/>
-      <c r="F304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -5302,8 +4690,6 @@
       <c r="D305" t="n">
         <v>6</v>
       </c>
-      <c r="E305" t="inlineStr"/>
-      <c r="F305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -5318,8 +4704,6 @@
       <c r="D306" t="n">
         <v>6</v>
       </c>
-      <c r="E306" t="inlineStr"/>
-      <c r="F306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -5334,8 +4718,6 @@
       <c r="D307" t="n">
         <v>6</v>
       </c>
-      <c r="E307" t="inlineStr"/>
-      <c r="F307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -5350,8 +4732,11 @@
       <c r="D308" t="n">
         <v>6</v>
       </c>
-      <c r="E308" t="inlineStr"/>
-      <c r="F308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -5366,8 +4751,6 @@
       <c r="D309" t="n">
         <v>7</v>
       </c>
-      <c r="E309" t="inlineStr"/>
-      <c r="F309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -5382,8 +4765,6 @@
       <c r="D310" t="n">
         <v>7</v>
       </c>
-      <c r="E310" t="inlineStr"/>
-      <c r="F310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -5398,8 +4779,6 @@
       <c r="D311" t="n">
         <v>7</v>
       </c>
-      <c r="E311" t="inlineStr"/>
-      <c r="F311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -5414,8 +4793,6 @@
       <c r="D312" t="n">
         <v>7</v>
       </c>
-      <c r="E312" t="inlineStr"/>
-      <c r="F312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -5430,8 +4807,6 @@
       <c r="D313" t="n">
         <v>7</v>
       </c>
-      <c r="E313" t="inlineStr"/>
-      <c r="F313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -5446,8 +4821,6 @@
       <c r="D314" t="n">
         <v>7</v>
       </c>
-      <c r="E314" t="inlineStr"/>
-      <c r="F314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -5462,8 +4835,6 @@
       <c r="D315" t="n">
         <v>7</v>
       </c>
-      <c r="E315" t="inlineStr"/>
-      <c r="F315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -5478,8 +4849,6 @@
       <c r="D316" t="n">
         <v>7</v>
       </c>
-      <c r="E316" t="inlineStr"/>
-      <c r="F316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -5494,8 +4863,6 @@
       <c r="D317" t="n">
         <v>7</v>
       </c>
-      <c r="E317" t="inlineStr"/>
-      <c r="F317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -5510,8 +4877,6 @@
       <c r="D318" t="n">
         <v>7</v>
       </c>
-      <c r="E318" t="inlineStr"/>
-      <c r="F318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -5526,8 +4891,6 @@
       <c r="D319" t="n">
         <v>7</v>
       </c>
-      <c r="E319" t="inlineStr"/>
-      <c r="F319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -5542,8 +4905,6 @@
       <c r="D320" t="n">
         <v>7</v>
       </c>
-      <c r="E320" t="inlineStr"/>
-      <c r="F320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -5558,8 +4919,6 @@
       <c r="D321" t="n">
         <v>7</v>
       </c>
-      <c r="E321" t="inlineStr"/>
-      <c r="F321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -5574,8 +4933,6 @@
       <c r="D322" t="n">
         <v>7</v>
       </c>
-      <c r="E322" t="inlineStr"/>
-      <c r="F322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -5590,8 +4947,6 @@
       <c r="D323" t="n">
         <v>7</v>
       </c>
-      <c r="E323" t="inlineStr"/>
-      <c r="F323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -5606,8 +4961,6 @@
       <c r="D324" t="n">
         <v>7</v>
       </c>
-      <c r="E324" t="inlineStr"/>
-      <c r="F324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -5622,8 +4975,6 @@
       <c r="D325" t="n">
         <v>7</v>
       </c>
-      <c r="E325" t="inlineStr"/>
-      <c r="F325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -5638,8 +4989,6 @@
       <c r="D326" t="n">
         <v>7</v>
       </c>
-      <c r="E326" t="inlineStr"/>
-      <c r="F326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5654,8 +5003,6 @@
       <c r="D327" t="n">
         <v>7</v>
       </c>
-      <c r="E327" t="inlineStr"/>
-      <c r="F327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5670,8 +5017,6 @@
       <c r="D328" t="n">
         <v>7</v>
       </c>
-      <c r="E328" t="inlineStr"/>
-      <c r="F328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5686,8 +5031,6 @@
       <c r="D329" t="n">
         <v>7</v>
       </c>
-      <c r="E329" t="inlineStr"/>
-      <c r="F329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5702,8 +5045,6 @@
       <c r="D330" t="n">
         <v>7</v>
       </c>
-      <c r="E330" t="inlineStr"/>
-      <c r="F330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5718,8 +5059,6 @@
       <c r="D331" t="n">
         <v>7</v>
       </c>
-      <c r="E331" t="inlineStr"/>
-      <c r="F331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5734,8 +5073,6 @@
       <c r="D332" t="n">
         <v>7</v>
       </c>
-      <c r="E332" t="inlineStr"/>
-      <c r="F332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5750,8 +5087,6 @@
       <c r="D333" t="n">
         <v>7</v>
       </c>
-      <c r="E333" t="inlineStr"/>
-      <c r="F333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5766,8 +5101,6 @@
       <c r="D334" t="n">
         <v>7</v>
       </c>
-      <c r="E334" t="inlineStr"/>
-      <c r="F334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5782,8 +5115,6 @@
       <c r="D335" t="n">
         <v>7</v>
       </c>
-      <c r="E335" t="inlineStr"/>
-      <c r="F335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5798,8 +5129,6 @@
       <c r="D336" t="n">
         <v>7</v>
       </c>
-      <c r="E336" t="inlineStr"/>
-      <c r="F336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5814,8 +5143,6 @@
       <c r="D337" t="n">
         <v>7</v>
       </c>
-      <c r="E337" t="inlineStr"/>
-      <c r="F337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5830,8 +5157,6 @@
       <c r="D338" t="n">
         <v>7</v>
       </c>
-      <c r="E338" t="inlineStr"/>
-      <c r="F338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5846,8 +5171,6 @@
       <c r="D339" t="n">
         <v>7</v>
       </c>
-      <c r="E339" t="inlineStr"/>
-      <c r="F339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5862,8 +5185,6 @@
       <c r="D340" t="n">
         <v>7</v>
       </c>
-      <c r="E340" t="inlineStr"/>
-      <c r="F340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5878,8 +5199,6 @@
       <c r="D341" t="n">
         <v>7</v>
       </c>
-      <c r="E341" t="inlineStr"/>
-      <c r="F341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5894,8 +5213,6 @@
       <c r="D342" t="n">
         <v>7</v>
       </c>
-      <c r="E342" t="inlineStr"/>
-      <c r="F342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5910,8 +5227,6 @@
       <c r="D343" t="n">
         <v>7</v>
       </c>
-      <c r="E343" t="inlineStr"/>
-      <c r="F343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5926,8 +5241,6 @@
       <c r="D344" t="n">
         <v>7</v>
       </c>
-      <c r="E344" t="inlineStr"/>
-      <c r="F344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5942,8 +5255,6 @@
       <c r="D345" t="n">
         <v>7</v>
       </c>
-      <c r="E345" t="inlineStr"/>
-      <c r="F345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -5958,8 +5269,6 @@
       <c r="D346" t="n">
         <v>7</v>
       </c>
-      <c r="E346" t="inlineStr"/>
-      <c r="F346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -5974,8 +5283,6 @@
       <c r="D347" t="n">
         <v>7</v>
       </c>
-      <c r="E347" t="inlineStr"/>
-      <c r="F347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -5990,8 +5297,6 @@
       <c r="D348" t="n">
         <v>7</v>
       </c>
-      <c r="E348" t="inlineStr"/>
-      <c r="F348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -6006,8 +5311,6 @@
       <c r="D349" t="n">
         <v>7</v>
       </c>
-      <c r="E349" t="inlineStr"/>
-      <c r="F349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -6022,8 +5325,6 @@
       <c r="D350" t="n">
         <v>7</v>
       </c>
-      <c r="E350" t="inlineStr"/>
-      <c r="F350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -6038,8 +5339,6 @@
       <c r="D351" t="n">
         <v>7</v>
       </c>
-      <c r="E351" t="inlineStr"/>
-      <c r="F351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -6054,8 +5353,6 @@
       <c r="D352" t="n">
         <v>7</v>
       </c>
-      <c r="E352" t="inlineStr"/>
-      <c r="F352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -6070,8 +5367,6 @@
       <c r="D353" t="n">
         <v>7</v>
       </c>
-      <c r="E353" t="inlineStr"/>
-      <c r="F353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -6086,8 +5381,6 @@
       <c r="D354" t="n">
         <v>7</v>
       </c>
-      <c r="E354" t="inlineStr"/>
-      <c r="F354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -6102,8 +5395,6 @@
       <c r="D355" t="n">
         <v>7</v>
       </c>
-      <c r="E355" t="inlineStr"/>
-      <c r="F355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -6118,8 +5409,6 @@
       <c r="D356" t="n">
         <v>7</v>
       </c>
-      <c r="E356" t="inlineStr"/>
-      <c r="F356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -6134,8 +5423,6 @@
       <c r="D357" t="n">
         <v>7</v>
       </c>
-      <c r="E357" t="inlineStr"/>
-      <c r="F357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -6150,8 +5437,6 @@
       <c r="D358" t="n">
         <v>7</v>
       </c>
-      <c r="E358" t="inlineStr"/>
-      <c r="F358" t="inlineStr"/>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -6166,8 +5451,6 @@
       <c r="D359" t="n">
         <v>8</v>
       </c>
-      <c r="E359" t="inlineStr"/>
-      <c r="F359" t="inlineStr"/>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -6182,8 +5465,6 @@
       <c r="D360" t="n">
         <v>8</v>
       </c>
-      <c r="E360" t="inlineStr"/>
-      <c r="F360" t="inlineStr"/>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -6198,8 +5479,6 @@
       <c r="D361" t="n">
         <v>8</v>
       </c>
-      <c r="E361" t="inlineStr"/>
-      <c r="F361" t="inlineStr"/>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -6214,8 +5493,6 @@
       <c r="D362" t="n">
         <v>8</v>
       </c>
-      <c r="E362" t="inlineStr"/>
-      <c r="F362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -6230,8 +5507,6 @@
       <c r="D363" t="n">
         <v>8</v>
       </c>
-      <c r="E363" t="inlineStr"/>
-      <c r="F363" t="inlineStr"/>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -6246,8 +5521,6 @@
       <c r="D364" t="n">
         <v>8</v>
       </c>
-      <c r="E364" t="inlineStr"/>
-      <c r="F364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -6262,8 +5535,6 @@
       <c r="D365" t="n">
         <v>8</v>
       </c>
-      <c r="E365" t="inlineStr"/>
-      <c r="F365" t="inlineStr"/>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -6278,8 +5549,6 @@
       <c r="D366" t="n">
         <v>8</v>
       </c>
-      <c r="E366" t="inlineStr"/>
-      <c r="F366" t="inlineStr"/>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -6294,8 +5563,6 @@
       <c r="D367" t="n">
         <v>8</v>
       </c>
-      <c r="E367" t="inlineStr"/>
-      <c r="F367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -6310,8 +5577,6 @@
       <c r="D368" t="n">
         <v>8</v>
       </c>
-      <c r="E368" t="inlineStr"/>
-      <c r="F368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -6326,8 +5591,6 @@
       <c r="D369" t="n">
         <v>8</v>
       </c>
-      <c r="E369" t="inlineStr"/>
-      <c r="F369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -6342,8 +5605,6 @@
       <c r="D370" t="n">
         <v>8</v>
       </c>
-      <c r="E370" t="inlineStr"/>
-      <c r="F370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -6358,8 +5619,6 @@
       <c r="D371" t="n">
         <v>8</v>
       </c>
-      <c r="E371" t="inlineStr"/>
-      <c r="F371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -6374,8 +5633,6 @@
       <c r="D372" t="n">
         <v>8</v>
       </c>
-      <c r="E372" t="inlineStr"/>
-      <c r="F372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -6390,8 +5647,6 @@
       <c r="D373" t="n">
         <v>8</v>
       </c>
-      <c r="E373" t="inlineStr"/>
-      <c r="F373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -6406,8 +5661,6 @@
       <c r="D374" t="n">
         <v>8</v>
       </c>
-      <c r="E374" t="inlineStr"/>
-      <c r="F374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -6422,8 +5675,6 @@
       <c r="D375" t="n">
         <v>8</v>
       </c>
-      <c r="E375" t="inlineStr"/>
-      <c r="F375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -6438,8 +5689,6 @@
       <c r="D376" t="n">
         <v>8</v>
       </c>
-      <c r="E376" t="inlineStr"/>
-      <c r="F376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -6454,8 +5703,6 @@
       <c r="D377" t="n">
         <v>8</v>
       </c>
-      <c r="E377" t="inlineStr"/>
-      <c r="F377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -6470,8 +5717,6 @@
       <c r="D378" t="n">
         <v>8</v>
       </c>
-      <c r="E378" t="inlineStr"/>
-      <c r="F378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -6486,8 +5731,6 @@
       <c r="D379" t="n">
         <v>8</v>
       </c>
-      <c r="E379" t="inlineStr"/>
-      <c r="F379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -6502,8 +5745,6 @@
       <c r="D380" t="n">
         <v>8</v>
       </c>
-      <c r="E380" t="inlineStr"/>
-      <c r="F380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -6518,8 +5759,6 @@
       <c r="D381" t="n">
         <v>8</v>
       </c>
-      <c r="E381" t="inlineStr"/>
-      <c r="F381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -6534,8 +5773,6 @@
       <c r="D382" t="n">
         <v>8</v>
       </c>
-      <c r="E382" t="inlineStr"/>
-      <c r="F382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -6550,8 +5787,6 @@
       <c r="D383" t="n">
         <v>8</v>
       </c>
-      <c r="E383" t="inlineStr"/>
-      <c r="F383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -6566,8 +5801,6 @@
       <c r="D384" t="n">
         <v>8</v>
       </c>
-      <c r="E384" t="inlineStr"/>
-      <c r="F384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -6582,8 +5815,6 @@
       <c r="D385" t="n">
         <v>8</v>
       </c>
-      <c r="E385" t="inlineStr"/>
-      <c r="F385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -6598,8 +5829,6 @@
       <c r="D386" t="n">
         <v>8</v>
       </c>
-      <c r="E386" t="inlineStr"/>
-      <c r="F386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -6614,8 +5843,6 @@
       <c r="D387" t="n">
         <v>8</v>
       </c>
-      <c r="E387" t="inlineStr"/>
-      <c r="F387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -6630,8 +5857,6 @@
       <c r="D388" t="n">
         <v>8</v>
       </c>
-      <c r="E388" t="inlineStr"/>
-      <c r="F388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -6646,8 +5871,6 @@
       <c r="D389" t="n">
         <v>8</v>
       </c>
-      <c r="E389" t="inlineStr"/>
-      <c r="F389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -6662,8 +5885,6 @@
       <c r="D390" t="n">
         <v>8</v>
       </c>
-      <c r="E390" t="inlineStr"/>
-      <c r="F390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -6678,8 +5899,6 @@
       <c r="D391" t="n">
         <v>8</v>
       </c>
-      <c r="E391" t="inlineStr"/>
-      <c r="F391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -6694,8 +5913,6 @@
       <c r="D392" t="n">
         <v>8</v>
       </c>
-      <c r="E392" t="inlineStr"/>
-      <c r="F392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -6710,8 +5927,6 @@
       <c r="D393" t="n">
         <v>8</v>
       </c>
-      <c r="E393" t="inlineStr"/>
-      <c r="F393" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -6726,8 +5941,6 @@
       <c r="D394" t="n">
         <v>8</v>
       </c>
-      <c r="E394" t="inlineStr"/>
-      <c r="F394" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -6742,8 +5955,6 @@
       <c r="D395" t="n">
         <v>8</v>
       </c>
-      <c r="E395" t="inlineStr"/>
-      <c r="F395" t="inlineStr"/>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -6758,8 +5969,6 @@
       <c r="D396" t="n">
         <v>8</v>
       </c>
-      <c r="E396" t="inlineStr"/>
-      <c r="F396" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -6774,8 +5983,6 @@
       <c r="D397" t="n">
         <v>8</v>
       </c>
-      <c r="E397" t="inlineStr"/>
-      <c r="F397" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -6790,8 +5997,6 @@
       <c r="D398" t="n">
         <v>8</v>
       </c>
-      <c r="E398" t="inlineStr"/>
-      <c r="F398" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -6806,8 +6011,6 @@
       <c r="D399" t="n">
         <v>8</v>
       </c>
-      <c r="E399" t="inlineStr"/>
-      <c r="F399" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -6822,8 +6025,6 @@
       <c r="D400" t="n">
         <v>8</v>
       </c>
-      <c r="E400" t="inlineStr"/>
-      <c r="F400" t="inlineStr"/>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -6838,8 +6039,6 @@
       <c r="D401" t="n">
         <v>8</v>
       </c>
-      <c r="E401" t="inlineStr"/>
-      <c r="F401" t="inlineStr"/>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -6854,8 +6053,6 @@
       <c r="D402" t="n">
         <v>8</v>
       </c>
-      <c r="E402" t="inlineStr"/>
-      <c r="F402" t="inlineStr"/>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -6870,8 +6067,6 @@
       <c r="D403" t="n">
         <v>8</v>
       </c>
-      <c r="E403" t="inlineStr"/>
-      <c r="F403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -6886,8 +6081,6 @@
       <c r="D404" t="n">
         <v>8</v>
       </c>
-      <c r="E404" t="inlineStr"/>
-      <c r="F404" t="inlineStr"/>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -6902,8 +6095,6 @@
       <c r="D405" t="n">
         <v>8</v>
       </c>
-      <c r="E405" t="inlineStr"/>
-      <c r="F405" t="inlineStr"/>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -6918,8 +6109,6 @@
       <c r="D406" t="n">
         <v>8</v>
       </c>
-      <c r="E406" t="inlineStr"/>
-      <c r="F406" t="inlineStr"/>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -6934,8 +6123,6 @@
       <c r="D407" t="n">
         <v>8</v>
       </c>
-      <c r="E407" t="inlineStr"/>
-      <c r="F407" t="inlineStr"/>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -6950,8 +6137,11 @@
       <c r="D408" t="n">
         <v>8</v>
       </c>
-      <c r="E408" t="inlineStr"/>
-      <c r="F408" t="inlineStr"/>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>tutorial</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -6966,8 +6156,6 @@
       <c r="D409" t="n">
         <v>9</v>
       </c>
-      <c r="E409" t="inlineStr"/>
-      <c r="F409" t="inlineStr"/>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -6982,8 +6170,6 @@
       <c r="D410" t="n">
         <v>9</v>
       </c>
-      <c r="E410" t="inlineStr"/>
-      <c r="F410" t="inlineStr"/>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -6998,8 +6184,6 @@
       <c r="D411" t="n">
         <v>9</v>
       </c>
-      <c r="E411" t="inlineStr"/>
-      <c r="F411" t="inlineStr"/>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -7014,8 +6198,6 @@
       <c r="D412" t="n">
         <v>9</v>
       </c>
-      <c r="E412" t="inlineStr"/>
-      <c r="F412" t="inlineStr"/>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -7030,8 +6212,6 @@
       <c r="D413" t="n">
         <v>9</v>
       </c>
-      <c r="E413" t="inlineStr"/>
-      <c r="F413" t="inlineStr"/>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -7046,8 +6226,6 @@
       <c r="D414" t="n">
         <v>9</v>
       </c>
-      <c r="E414" t="inlineStr"/>
-      <c r="F414" t="inlineStr"/>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -7062,8 +6240,6 @@
       <c r="D415" t="n">
         <v>9</v>
       </c>
-      <c r="E415" t="inlineStr"/>
-      <c r="F415" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -7078,8 +6254,6 @@
       <c r="D416" t="n">
         <v>9</v>
       </c>
-      <c r="E416" t="inlineStr"/>
-      <c r="F416" t="inlineStr"/>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -7094,8 +6268,6 @@
       <c r="D417" t="n">
         <v>9</v>
       </c>
-      <c r="E417" t="inlineStr"/>
-      <c r="F417" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -7110,8 +6282,6 @@
       <c r="D418" t="n">
         <v>9</v>
       </c>
-      <c r="E418" t="inlineStr"/>
-      <c r="F418" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -7126,8 +6296,6 @@
       <c r="D419" t="n">
         <v>9</v>
       </c>
-      <c r="E419" t="inlineStr"/>
-      <c r="F419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -7142,8 +6310,6 @@
       <c r="D420" t="n">
         <v>9</v>
       </c>
-      <c r="E420" t="inlineStr"/>
-      <c r="F420" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -7158,8 +6324,6 @@
       <c r="D421" t="n">
         <v>9</v>
       </c>
-      <c r="E421" t="inlineStr"/>
-      <c r="F421" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -7174,8 +6338,6 @@
       <c r="D422" t="n">
         <v>9</v>
       </c>
-      <c r="E422" t="inlineStr"/>
-      <c r="F422" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -7190,8 +6352,6 @@
       <c r="D423" t="n">
         <v>9</v>
       </c>
-      <c r="E423" t="inlineStr"/>
-      <c r="F423" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -7206,8 +6366,6 @@
       <c r="D424" t="n">
         <v>9</v>
       </c>
-      <c r="E424" t="inlineStr"/>
-      <c r="F424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -7222,8 +6380,6 @@
       <c r="D425" t="n">
         <v>9</v>
       </c>
-      <c r="E425" t="inlineStr"/>
-      <c r="F425" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -7238,8 +6394,6 @@
       <c r="D426" t="n">
         <v>9</v>
       </c>
-      <c r="E426" t="inlineStr"/>
-      <c r="F426" t="inlineStr"/>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -7254,8 +6408,6 @@
       <c r="D427" t="n">
         <v>9</v>
       </c>
-      <c r="E427" t="inlineStr"/>
-      <c r="F427" t="inlineStr"/>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -7270,8 +6422,6 @@
       <c r="D428" t="n">
         <v>9</v>
       </c>
-      <c r="E428" t="inlineStr"/>
-      <c r="F428" t="inlineStr"/>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -7286,8 +6436,6 @@
       <c r="D429" t="n">
         <v>9</v>
       </c>
-      <c r="E429" t="inlineStr"/>
-      <c r="F429" t="inlineStr"/>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -7302,8 +6450,6 @@
       <c r="D430" t="n">
         <v>9</v>
       </c>
-      <c r="E430" t="inlineStr"/>
-      <c r="F430" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -7318,8 +6464,6 @@
       <c r="D431" t="n">
         <v>9</v>
       </c>
-      <c r="E431" t="inlineStr"/>
-      <c r="F431" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -7334,8 +6478,6 @@
       <c r="D432" t="n">
         <v>9</v>
       </c>
-      <c r="E432" t="inlineStr"/>
-      <c r="F432" t="inlineStr"/>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -7350,8 +6492,6 @@
       <c r="D433" t="n">
         <v>9</v>
       </c>
-      <c r="E433" t="inlineStr"/>
-      <c r="F433" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -7366,8 +6506,6 @@
       <c r="D434" t="n">
         <v>9</v>
       </c>
-      <c r="E434" t="inlineStr"/>
-      <c r="F434" t="inlineStr"/>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -7382,8 +6520,6 @@
       <c r="D435" t="n">
         <v>9</v>
       </c>
-      <c r="E435" t="inlineStr"/>
-      <c r="F435" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -7398,8 +6534,6 @@
       <c r="D436" t="n">
         <v>9</v>
       </c>
-      <c r="E436" t="inlineStr"/>
-      <c r="F436" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -7414,8 +6548,6 @@
       <c r="D437" t="n">
         <v>9</v>
       </c>
-      <c r="E437" t="inlineStr"/>
-      <c r="F437" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -7430,8 +6562,6 @@
       <c r="D438" t="n">
         <v>9</v>
       </c>
-      <c r="E438" t="inlineStr"/>
-      <c r="F438" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -7446,8 +6576,6 @@
       <c r="D439" t="n">
         <v>9</v>
       </c>
-      <c r="E439" t="inlineStr"/>
-      <c r="F439" t="inlineStr"/>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -7462,8 +6590,6 @@
       <c r="D440" t="n">
         <v>9</v>
       </c>
-      <c r="E440" t="inlineStr"/>
-      <c r="F440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -7478,8 +6604,6 @@
       <c r="D441" t="n">
         <v>9</v>
       </c>
-      <c r="E441" t="inlineStr"/>
-      <c r="F441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -7494,8 +6618,6 @@
       <c r="D442" t="n">
         <v>9</v>
       </c>
-      <c r="E442" t="inlineStr"/>
-      <c r="F442" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -7510,8 +6632,6 @@
       <c r="D443" t="n">
         <v>9</v>
       </c>
-      <c r="E443" t="inlineStr"/>
-      <c r="F443" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -7526,8 +6646,6 @@
       <c r="D444" t="n">
         <v>9</v>
       </c>
-      <c r="E444" t="inlineStr"/>
-      <c r="F444" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -7542,8 +6660,6 @@
       <c r="D445" t="n">
         <v>9</v>
       </c>
-      <c r="E445" t="inlineStr"/>
-      <c r="F445" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -7558,8 +6674,6 @@
       <c r="D446" t="n">
         <v>9</v>
       </c>
-      <c r="E446" t="inlineStr"/>
-      <c r="F446" t="inlineStr"/>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -7574,8 +6688,6 @@
       <c r="D447" t="n">
         <v>9</v>
       </c>
-      <c r="E447" t="inlineStr"/>
-      <c r="F447" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -7590,8 +6702,6 @@
       <c r="D448" t="n">
         <v>9</v>
       </c>
-      <c r="E448" t="inlineStr"/>
-      <c r="F448" t="inlineStr"/>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -7606,8 +6716,6 @@
       <c r="D449" t="n">
         <v>9</v>
       </c>
-      <c r="E449" t="inlineStr"/>
-      <c r="F449" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -7622,8 +6730,6 @@
       <c r="D450" t="n">
         <v>9</v>
       </c>
-      <c r="E450" t="inlineStr"/>
-      <c r="F450" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -7638,8 +6744,6 @@
       <c r="D451" t="n">
         <v>9</v>
       </c>
-      <c r="E451" t="inlineStr"/>
-      <c r="F451" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -7654,8 +6758,6 @@
       <c r="D452" t="n">
         <v>9</v>
       </c>
-      <c r="E452" t="inlineStr"/>
-      <c r="F452" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -7670,8 +6772,6 @@
       <c r="D453" t="n">
         <v>9</v>
       </c>
-      <c r="E453" t="inlineStr"/>
-      <c r="F453" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -7686,8 +6786,6 @@
       <c r="D454" t="n">
         <v>9</v>
       </c>
-      <c r="E454" t="inlineStr"/>
-      <c r="F454" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -7702,8 +6800,6 @@
       <c r="D455" t="n">
         <v>9</v>
       </c>
-      <c r="E455" t="inlineStr"/>
-      <c r="F455" t="inlineStr"/>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -7718,8 +6814,6 @@
       <c r="D456" t="n">
         <v>9</v>
       </c>
-      <c r="E456" t="inlineStr"/>
-      <c r="F456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -7734,8 +6828,6 @@
       <c r="D457" t="n">
         <v>9</v>
       </c>
-      <c r="E457" t="inlineStr"/>
-      <c r="F457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -7750,8 +6842,6 @@
       <c r="D458" t="n">
         <v>9</v>
       </c>
-      <c r="E458" t="inlineStr"/>
-      <c r="F458" t="inlineStr"/>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -7766,8 +6856,6 @@
       <c r="D459" t="n">
         <v>10</v>
       </c>
-      <c r="E459" t="inlineStr"/>
-      <c r="F459" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -7782,8 +6870,6 @@
       <c r="D460" t="n">
         <v>10</v>
       </c>
-      <c r="E460" t="inlineStr"/>
-      <c r="F460" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -7798,8 +6884,6 @@
       <c r="D461" t="n">
         <v>10</v>
       </c>
-      <c r="E461" t="inlineStr"/>
-      <c r="F461" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -7814,8 +6898,6 @@
       <c r="D462" t="n">
         <v>10</v>
       </c>
-      <c r="E462" t="inlineStr"/>
-      <c r="F462" t="inlineStr"/>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -7830,8 +6912,6 @@
       <c r="D463" t="n">
         <v>10</v>
       </c>
-      <c r="E463" t="inlineStr"/>
-      <c r="F463" t="inlineStr"/>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -7846,8 +6926,6 @@
       <c r="D464" t="n">
         <v>10</v>
       </c>
-      <c r="E464" t="inlineStr"/>
-      <c r="F464" t="inlineStr"/>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -7862,8 +6940,6 @@
       <c r="D465" t="n">
         <v>10</v>
       </c>
-      <c r="E465" t="inlineStr"/>
-      <c r="F465" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -7878,8 +6954,6 @@
       <c r="D466" t="n">
         <v>10</v>
       </c>
-      <c r="E466" t="inlineStr"/>
-      <c r="F466" t="inlineStr"/>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -7894,8 +6968,6 @@
       <c r="D467" t="n">
         <v>10</v>
       </c>
-      <c r="E467" t="inlineStr"/>
-      <c r="F467" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -7910,8 +6982,6 @@
       <c r="D468" t="n">
         <v>10</v>
       </c>
-      <c r="E468" t="inlineStr"/>
-      <c r="F468" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -7926,8 +6996,6 @@
       <c r="D469" t="n">
         <v>10</v>
       </c>
-      <c r="E469" t="inlineStr"/>
-      <c r="F469" t="inlineStr"/>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -7942,8 +7010,6 @@
       <c r="D470" t="n">
         <v>10</v>
       </c>
-      <c r="E470" t="inlineStr"/>
-      <c r="F470" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -7958,8 +7024,6 @@
       <c r="D471" t="n">
         <v>10</v>
       </c>
-      <c r="E471" t="inlineStr"/>
-      <c r="F471" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -7974,8 +7038,6 @@
       <c r="D472" t="n">
         <v>10</v>
       </c>
-      <c r="E472" t="inlineStr"/>
-      <c r="F472" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -7990,8 +7052,6 @@
       <c r="D473" t="n">
         <v>10</v>
       </c>
-      <c r="E473" t="inlineStr"/>
-      <c r="F473" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -8006,8 +7066,6 @@
       <c r="D474" t="n">
         <v>10</v>
       </c>
-      <c r="E474" t="inlineStr"/>
-      <c r="F474" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -8022,8 +7080,6 @@
       <c r="D475" t="n">
         <v>10</v>
       </c>
-      <c r="E475" t="inlineStr"/>
-      <c r="F475" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -8038,8 +7094,6 @@
       <c r="D476" t="n">
         <v>10</v>
       </c>
-      <c r="E476" t="inlineStr"/>
-      <c r="F476" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -8054,8 +7108,6 @@
       <c r="D477" t="n">
         <v>10</v>
       </c>
-      <c r="E477" t="inlineStr"/>
-      <c r="F477" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -8070,8 +7122,6 @@
       <c r="D478" t="n">
         <v>10</v>
       </c>
-      <c r="E478" t="inlineStr"/>
-      <c r="F478" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -8086,8 +7136,6 @@
       <c r="D479" t="n">
         <v>10</v>
       </c>
-      <c r="E479" t="inlineStr"/>
-      <c r="F479" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -8102,8 +7150,6 @@
       <c r="D480" t="n">
         <v>10</v>
       </c>
-      <c r="E480" t="inlineStr"/>
-      <c r="F480" t="inlineStr"/>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -8118,8 +7164,6 @@
       <c r="D481" t="n">
         <v>10</v>
       </c>
-      <c r="E481" t="inlineStr"/>
-      <c r="F481" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -8134,8 +7178,6 @@
       <c r="D482" t="n">
         <v>10</v>
       </c>
-      <c r="E482" t="inlineStr"/>
-      <c r="F482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -8150,8 +7192,6 @@
       <c r="D483" t="n">
         <v>10</v>
       </c>
-      <c r="E483" t="inlineStr"/>
-      <c r="F483" t="inlineStr"/>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -8166,8 +7206,6 @@
       <c r="D484" t="n">
         <v>10</v>
       </c>
-      <c r="E484" t="inlineStr"/>
-      <c r="F484" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -8182,8 +7220,6 @@
       <c r="D485" t="n">
         <v>10</v>
       </c>
-      <c r="E485" t="inlineStr"/>
-      <c r="F485" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -8198,8 +7234,6 @@
       <c r="D486" t="n">
         <v>10</v>
       </c>
-      <c r="E486" t="inlineStr"/>
-      <c r="F486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -8214,8 +7248,6 @@
       <c r="D487" t="n">
         <v>10</v>
       </c>
-      <c r="E487" t="inlineStr"/>
-      <c r="F487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -8230,8 +7262,6 @@
       <c r="D488" t="n">
         <v>10</v>
       </c>
-      <c r="E488" t="inlineStr"/>
-      <c r="F488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -8246,8 +7276,6 @@
       <c r="D489" t="n">
         <v>10</v>
       </c>
-      <c r="E489" t="inlineStr"/>
-      <c r="F489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -8262,8 +7290,6 @@
       <c r="D490" t="n">
         <v>10</v>
       </c>
-      <c r="E490" t="inlineStr"/>
-      <c r="F490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -8278,8 +7304,6 @@
       <c r="D491" t="n">
         <v>10</v>
       </c>
-      <c r="E491" t="inlineStr"/>
-      <c r="F491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -8294,8 +7318,6 @@
       <c r="D492" t="n">
         <v>10</v>
       </c>
-      <c r="E492" t="inlineStr"/>
-      <c r="F492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -8310,8 +7332,6 @@
       <c r="D493" t="n">
         <v>10</v>
       </c>
-      <c r="E493" t="inlineStr"/>
-      <c r="F493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -8326,8 +7346,6 @@
       <c r="D494" t="n">
         <v>10</v>
       </c>
-      <c r="E494" t="inlineStr"/>
-      <c r="F494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -8342,8 +7360,6 @@
       <c r="D495" t="n">
         <v>10</v>
       </c>
-      <c r="E495" t="inlineStr"/>
-      <c r="F495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -8358,8 +7374,6 @@
       <c r="D496" t="n">
         <v>10</v>
       </c>
-      <c r="E496" t="inlineStr"/>
-      <c r="F496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -8374,8 +7388,6 @@
       <c r="D497" t="n">
         <v>10</v>
       </c>
-      <c r="E497" t="inlineStr"/>
-      <c r="F497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -8390,8 +7402,6 @@
       <c r="D498" t="n">
         <v>10</v>
       </c>
-      <c r="E498" t="inlineStr"/>
-      <c r="F498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -8406,8 +7416,6 @@
       <c r="D499" t="n">
         <v>10</v>
       </c>
-      <c r="E499" t="inlineStr"/>
-      <c r="F499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -8422,8 +7430,6 @@
       <c r="D500" t="n">
         <v>10</v>
       </c>
-      <c r="E500" t="inlineStr"/>
-      <c r="F500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -8438,8 +7444,6 @@
       <c r="D501" t="n">
         <v>10</v>
       </c>
-      <c r="E501" t="inlineStr"/>
-      <c r="F501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -8454,8 +7458,6 @@
       <c r="D502" t="n">
         <v>10</v>
       </c>
-      <c r="E502" t="inlineStr"/>
-      <c r="F502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -8470,8 +7472,6 @@
       <c r="D503" t="n">
         <v>10</v>
       </c>
-      <c r="E503" t="inlineStr"/>
-      <c r="F503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -8486,8 +7486,6 @@
       <c r="D504" t="n">
         <v>10</v>
       </c>
-      <c r="E504" t="inlineStr"/>
-      <c r="F504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -8502,8 +7500,6 @@
       <c r="D505" t="n">
         <v>10</v>
       </c>
-      <c r="E505" t="inlineStr"/>
-      <c r="F505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -8518,8 +7514,6 @@
       <c r="D506" t="n">
         <v>10</v>
       </c>
-      <c r="E506" t="inlineStr"/>
-      <c r="F506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -8534,8 +7528,6 @@
       <c r="D507" t="n">
         <v>10</v>
       </c>
-      <c r="E507" t="inlineStr"/>
-      <c r="F507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -8550,8 +7542,6 @@
       <c r="D508" t="n">
         <v>10</v>
       </c>
-      <c r="E508" t="inlineStr"/>
-      <c r="F508" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8633,36 +7623,11 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -8674,7 +7639,6 @@
           <t>slice</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>SliceList 全切到 v2 复合变体</t>
@@ -8692,7 +7656,6 @@
           <t>level</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>对手 5 星 + 全胜阈值</t>
@@ -8710,7 +7673,6 @@
           <t>slice</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>末位强制 corner v2</t>
@@ -8772,7 +7734,6 @@
           <t>level</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>门票消耗 0</t>
@@ -8790,7 +7751,6 @@
           <t>slice</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>末位强制 goalkeep v2</t>
@@ -8940,7 +7900,6 @@
           <t>slice</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>保证至少 1 free_kick + 1 penalty</t>

--- a/output/test-config/level-tags/LevelTagCfg.xlsx
+++ b/output/test-config/level-tags/LevelTagCfg.xlsx
@@ -513,11 +513,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="n">
         <v>1</v>
@@ -531,6 +526,16 @@
       <c r="D9" t="n">
         <v>1</v>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tutorial, free_run</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -545,6 +550,12 @@
       <c r="D10" t="n">
         <v>1</v>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -559,6 +570,12 @@
       <c r="D11" t="n">
         <v>1</v>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -573,6 +590,12 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -587,6 +610,12 @@
       <c r="D13" t="n">
         <v>1</v>
       </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>默认:首段小高潮留给基础 tier,避免过早复杂化</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -601,6 +630,16 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -615,6 +654,12 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -629,6 +674,16 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -643,6 +698,12 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -657,6 +718,12 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -671,6 +738,16 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -685,6 +762,12 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -699,6 +782,12 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -713,6 +802,12 @@
       <c r="D22" t="n">
         <v>1</v>
       </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -727,6 +822,12 @@
       <c r="D23" t="n">
         <v>1</v>
       </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>默认:首段小高潮留给基础 tier,避免过早复杂化</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -741,6 +842,12 @@
       <c r="D24" t="n">
         <v>1</v>
       </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -755,6 +862,12 @@
       <c r="D25" t="n">
         <v>1</v>
       </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -769,6 +882,16 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -783,6 +906,12 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -797,6 +926,12 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -811,6 +946,16 @@
       <c r="D29" t="n">
         <v>1</v>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -825,6 +970,12 @@
       <c r="D30" t="n">
         <v>1</v>
       </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -839,6 +990,12 @@
       <c r="D31" t="n">
         <v>1</v>
       </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -853,6 +1010,12 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -867,6 +1030,12 @@
       <c r="D33" t="n">
         <v>1</v>
       </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>默认:首段小高潮留给基础 tier,避免过早复杂化</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -881,6 +1050,16 @@
       <c r="D34" t="n">
         <v>1</v>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -895,6 +1074,12 @@
       <c r="D35" t="n">
         <v>1</v>
       </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -909,6 +1094,16 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -923,6 +1118,12 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -937,6 +1138,12 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -951,6 +1158,16 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -965,6 +1182,12 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -979,6 +1202,12 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -993,6 +1222,12 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1007,6 +1242,12 @@
       <c r="D43" t="n">
         <v>1</v>
       </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>默认:首段小高潮留给基础 tier,避免过早复杂化</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1021,6 +1262,12 @@
       <c r="D44" t="n">
         <v>1</v>
       </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1035,6 +1282,12 @@
       <c r="D45" t="n">
         <v>1</v>
       </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1049,6 +1302,16 @@
       <c r="D46" t="n">
         <v>1</v>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1063,6 +1326,12 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1077,6 +1346,12 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1091,6 +1366,16 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1105,6 +1390,12 @@
       <c r="D50" t="n">
         <v>1</v>
       </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1119,6 +1410,12 @@
       <c r="D51" t="n">
         <v>1</v>
       </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1133,6 +1430,12 @@
       <c r="D52" t="n">
         <v>1</v>
       </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1147,6 +1450,12 @@
       <c r="D53" t="n">
         <v>1</v>
       </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>默认:首段小高潮留给基础 tier,避免过早复杂化</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1161,6 +1470,16 @@
       <c r="D54" t="n">
         <v>1</v>
       </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1175,6 +1494,12 @@
       <c r="D55" t="n">
         <v>1</v>
       </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1189,6 +1514,16 @@
       <c r="D56" t="n">
         <v>1</v>
       </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1203,6 +1538,12 @@
       <c r="D57" t="n">
         <v>1</v>
       </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1217,6 +1558,16 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>大段 Boss:阶段能力检验</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1231,6 +1582,16 @@
       <c r="D59" t="n">
         <v>2</v>
       </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1245,6 +1606,12 @@
       <c r="D60" t="n">
         <v>2</v>
       </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1259,6 +1626,12 @@
       <c r="D61" t="n">
         <v>2</v>
       </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1273,6 +1646,12 @@
       <c r="D62" t="n">
         <v>2</v>
       </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1287,6 +1666,16 @@
       <c r="D63" t="n">
         <v>2</v>
       </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1301,6 +1690,12 @@
       <c r="D64" t="n">
         <v>2</v>
       </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1315,6 +1710,12 @@
       <c r="D65" t="n">
         <v>2</v>
       </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1329,6 +1730,16 @@
       <c r="D66" t="n">
         <v>2</v>
       </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1343,6 +1754,12 @@
       <c r="D67" t="n">
         <v>2</v>
       </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1357,6 +1774,12 @@
       <c r="D68" t="n">
         <v>2</v>
       </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1371,6 +1794,16 @@
       <c r="D69" t="n">
         <v>2</v>
       </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1385,6 +1818,12 @@
       <c r="D70" t="n">
         <v>2</v>
       </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1399,6 +1838,12 @@
       <c r="D71" t="n">
         <v>2</v>
       </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1413,6 +1858,12 @@
       <c r="D72" t="n">
         <v>2</v>
       </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1427,6 +1878,16 @@
       <c r="D73" t="n">
         <v>2</v>
       </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1441,6 +1902,16 @@
       <c r="D74" t="n">
         <v>2</v>
       </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1455,6 +1926,12 @@
       <c r="D75" t="n">
         <v>2</v>
       </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1469,6 +1946,16 @@
       <c r="D76" t="n">
         <v>2</v>
       </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1483,6 +1970,12 @@
       <c r="D77" t="n">
         <v>2</v>
       </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1497,6 +1990,12 @@
       <c r="D78" t="n">
         <v>2</v>
       </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1511,6 +2010,16 @@
       <c r="D79" t="n">
         <v>2</v>
       </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1525,6 +2034,12 @@
       <c r="D80" t="n">
         <v>2</v>
       </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1539,6 +2054,12 @@
       <c r="D81" t="n">
         <v>2</v>
       </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1553,6 +2074,12 @@
       <c r="D82" t="n">
         <v>2</v>
       </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1567,6 +2094,16 @@
       <c r="D83" t="n">
         <v>2</v>
       </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1581,6 +2118,12 @@
       <c r="D84" t="n">
         <v>2</v>
       </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1595,6 +2138,12 @@
       <c r="D85" t="n">
         <v>2</v>
       </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1609,6 +2158,16 @@
       <c r="D86" t="n">
         <v>2</v>
       </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1623,6 +2182,12 @@
       <c r="D87" t="n">
         <v>2</v>
       </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1637,6 +2202,12 @@
       <c r="D88" t="n">
         <v>2</v>
       </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1651,6 +2222,16 @@
       <c r="D89" t="n">
         <v>2</v>
       </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1665,6 +2246,12 @@
       <c r="D90" t="n">
         <v>2</v>
       </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1679,6 +2266,12 @@
       <c r="D91" t="n">
         <v>2</v>
       </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1693,6 +2286,12 @@
       <c r="D92" t="n">
         <v>2</v>
       </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1707,6 +2306,16 @@
       <c r="D93" t="n">
         <v>2</v>
       </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1721,6 +2330,16 @@
       <c r="D94" t="n">
         <v>2</v>
       </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1735,6 +2354,12 @@
       <c r="D95" t="n">
         <v>2</v>
       </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1749,6 +2374,16 @@
       <c r="D96" t="n">
         <v>2</v>
       </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1763,6 +2398,12 @@
       <c r="D97" t="n">
         <v>2</v>
       </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1777,6 +2418,12 @@
       <c r="D98" t="n">
         <v>2</v>
       </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1791,6 +2438,16 @@
       <c r="D99" t="n">
         <v>2</v>
       </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>short_match, free_run</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>恢复:短局免票,给玩家重新进入心流</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1805,6 +2462,12 @@
       <c r="D100" t="n">
         <v>2</v>
       </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1819,6 +2482,12 @@
       <c r="D101" t="n">
         <v>2</v>
       </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1833,6 +2502,12 @@
       <c r="D102" t="n">
         <v>2</v>
       </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1847,6 +2522,16 @@
       <c r="D103" t="n">
         <v>2</v>
       </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1861,6 +2546,12 @@
       <c r="D104" t="n">
         <v>2</v>
       </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1875,6 +2566,12 @@
       <c r="D105" t="n">
         <v>2</v>
       </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1889,6 +2586,16 @@
       <c r="D106" t="n">
         <v>2</v>
       </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1903,6 +2610,12 @@
       <c r="D107" t="n">
         <v>2</v>
       </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -1922,6 +2635,11 @@
           <t>boss</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>大段 Boss:阶段能力检验</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1936,6 +2654,16 @@
       <c r="D109" t="n">
         <v>3</v>
       </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -1950,6 +2678,16 @@
       <c r="D110" t="n">
         <v>3</v>
       </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -1964,6 +2702,12 @@
       <c r="D111" t="n">
         <v>3</v>
       </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -1978,6 +2722,12 @@
       <c r="D112" t="n">
         <v>3</v>
       </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -1992,6 +2742,16 @@
       <c r="D113" t="n">
         <v>3</v>
       </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2006,6 +2766,16 @@
       <c r="D114" t="n">
         <v>3</v>
       </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2020,6 +2790,12 @@
       <c r="D115" t="n">
         <v>3</v>
       </c>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2034,6 +2810,16 @@
       <c r="D116" t="n">
         <v>3</v>
       </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2048,6 +2834,12 @@
       <c r="D117" t="n">
         <v>3</v>
       </c>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2062,6 +2854,12 @@
       <c r="D118" t="n">
         <v>3</v>
       </c>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2076,6 +2874,16 @@
       <c r="D119" t="n">
         <v>3</v>
       </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2090,6 +2898,16 @@
       <c r="D120" t="n">
         <v>3</v>
       </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2104,6 +2922,12 @@
       <c r="D121" t="n">
         <v>3</v>
       </c>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2118,6 +2942,12 @@
       <c r="D122" t="n">
         <v>3</v>
       </c>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2132,6 +2962,16 @@
       <c r="D123" t="n">
         <v>3</v>
       </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2146,6 +2986,12 @@
       <c r="D124" t="n">
         <v>3</v>
       </c>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2160,6 +3006,12 @@
       <c r="D125" t="n">
         <v>3</v>
       </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2174,6 +3026,16 @@
       <c r="D126" t="n">
         <v>3</v>
       </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2188,6 +3050,12 @@
       <c r="D127" t="n">
         <v>3</v>
       </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2202,6 +3070,12 @@
       <c r="D128" t="n">
         <v>3</v>
       </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2216,6 +3090,16 @@
       <c r="D129" t="n">
         <v>3</v>
       </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2230,6 +3114,16 @@
       <c r="D130" t="n">
         <v>3</v>
       </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2244,6 +3138,12 @@
       <c r="D131" t="n">
         <v>3</v>
       </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2258,6 +3158,12 @@
       <c r="D132" t="n">
         <v>3</v>
       </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2272,6 +3178,16 @@
       <c r="D133" t="n">
         <v>3</v>
       </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2286,6 +3202,16 @@
       <c r="D134" t="n">
         <v>3</v>
       </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2300,6 +3226,12 @@
       <c r="D135" t="n">
         <v>3</v>
       </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2314,6 +3246,16 @@
       <c r="D136" t="n">
         <v>3</v>
       </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2328,6 +3270,12 @@
       <c r="D137" t="n">
         <v>3</v>
       </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2342,6 +3290,12 @@
       <c r="D138" t="n">
         <v>3</v>
       </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2356,6 +3310,16 @@
       <c r="D139" t="n">
         <v>3</v>
       </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2370,6 +3334,16 @@
       <c r="D140" t="n">
         <v>3</v>
       </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2384,6 +3358,12 @@
       <c r="D141" t="n">
         <v>3</v>
       </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2398,6 +3378,12 @@
       <c r="D142" t="n">
         <v>3</v>
       </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2412,6 +3398,16 @@
       <c r="D143" t="n">
         <v>3</v>
       </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2426,6 +3422,12 @@
       <c r="D144" t="n">
         <v>3</v>
       </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2440,6 +3442,12 @@
       <c r="D145" t="n">
         <v>3</v>
       </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2454,6 +3462,16 @@
       <c r="D146" t="n">
         <v>3</v>
       </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2468,6 +3486,12 @@
       <c r="D147" t="n">
         <v>3</v>
       </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2482,6 +3506,12 @@
       <c r="D148" t="n">
         <v>3</v>
       </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>默认检验:保留 tier 基础节奏</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2496,6 +3526,16 @@
       <c r="D149" t="n">
         <v>3</v>
       </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2510,6 +3550,16 @@
       <c r="D150" t="n">
         <v>3</v>
       </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2524,6 +3574,12 @@
       <c r="D151" t="n">
         <v>3</v>
       </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2538,6 +3594,12 @@
       <c r="D152" t="n">
         <v>3</v>
       </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2552,6 +3614,16 @@
       <c r="D153" t="n">
         <v>3</v>
       </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2566,6 +3638,16 @@
       <c r="D154" t="n">
         <v>3</v>
       </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2580,6 +3662,12 @@
       <c r="D155" t="n">
         <v>3</v>
       </c>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2594,6 +3682,16 @@
       <c r="D156" t="n">
         <v>3</v>
       </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2608,6 +3706,12 @@
       <c r="D157" t="n">
         <v>3</v>
       </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2622,6 +3726,16 @@
       <c r="D158" t="n">
         <v>3</v>
       </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>大段 Boss:阶段能力检验</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2636,6 +3750,16 @@
       <c r="D159" t="n">
         <v>4</v>
       </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2650,6 +3774,16 @@
       <c r="D160" t="n">
         <v>4</v>
       </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2664,6 +3798,12 @@
       <c r="D161" t="n">
         <v>4</v>
       </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2678,6 +3818,12 @@
       <c r="D162" t="n">
         <v>4</v>
       </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2692,6 +3838,16 @@
       <c r="D163" t="n">
         <v>4</v>
       </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2706,6 +3862,12 @@
       <c r="D164" t="n">
         <v>4</v>
       </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2720,6 +3882,12 @@
       <c r="D165" t="n">
         <v>4</v>
       </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2734,6 +3902,16 @@
       <c r="D166" t="n">
         <v>4</v>
       </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2748,6 +3926,12 @@
       <c r="D167" t="n">
         <v>4</v>
       </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2762,6 +3946,16 @@
       <c r="D168" t="n">
         <v>4</v>
       </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2776,6 +3970,16 @@
       <c r="D169" t="n">
         <v>4</v>
       </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2790,6 +3994,16 @@
       <c r="D170" t="n">
         <v>4</v>
       </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2804,6 +4018,12 @@
       <c r="D171" t="n">
         <v>4</v>
       </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2818,6 +4038,12 @@
       <c r="D172" t="n">
         <v>4</v>
       </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2832,6 +4058,16 @@
       <c r="D173" t="n">
         <v>4</v>
       </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -2846,6 +4082,16 @@
       <c r="D174" t="n">
         <v>4</v>
       </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2860,6 +4106,12 @@
       <c r="D175" t="n">
         <v>4</v>
       </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2874,6 +4126,16 @@
       <c r="D176" t="n">
         <v>4</v>
       </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -2888,6 +4150,12 @@
       <c r="D177" t="n">
         <v>4</v>
       </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -2902,6 +4170,16 @@
       <c r="D178" t="n">
         <v>4</v>
       </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -2916,6 +4194,16 @@
       <c r="D179" t="n">
         <v>4</v>
       </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -2930,6 +4218,16 @@
       <c r="D180" t="n">
         <v>4</v>
       </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2944,6 +4242,12 @@
       <c r="D181" t="n">
         <v>4</v>
       </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -2958,6 +4262,12 @@
       <c r="D182" t="n">
         <v>4</v>
       </c>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2972,6 +4282,16 @@
       <c r="D183" t="n">
         <v>4</v>
       </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -2986,6 +4306,12 @@
       <c r="D184" t="n">
         <v>4</v>
       </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -3000,6 +4326,12 @@
       <c r="D185" t="n">
         <v>4</v>
       </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -3014,6 +4346,16 @@
       <c r="D186" t="n">
         <v>4</v>
       </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -3028,6 +4370,12 @@
       <c r="D187" t="n">
         <v>4</v>
       </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -3042,6 +4390,16 @@
       <c r="D188" t="n">
         <v>4</v>
       </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -3056,6 +4414,16 @@
       <c r="D189" t="n">
         <v>4</v>
       </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -3070,6 +4438,16 @@
       <c r="D190" t="n">
         <v>4</v>
       </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -3084,6 +4462,12 @@
       <c r="D191" t="n">
         <v>4</v>
       </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -3098,6 +4482,12 @@
       <c r="D192" t="n">
         <v>4</v>
       </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -3112,6 +4502,16 @@
       <c r="D193" t="n">
         <v>4</v>
       </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -3126,6 +4526,16 @@
       <c r="D194" t="n">
         <v>4</v>
       </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -3140,6 +4550,12 @@
       <c r="D195" t="n">
         <v>4</v>
       </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -3154,6 +4570,16 @@
       <c r="D196" t="n">
         <v>4</v>
       </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -3168,6 +4594,12 @@
       <c r="D197" t="n">
         <v>4</v>
       </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3182,6 +4614,16 @@
       <c r="D198" t="n">
         <v>4</v>
       </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3196,6 +4638,16 @@
       <c r="D199" t="n">
         <v>4</v>
       </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3210,6 +4662,16 @@
       <c r="D200" t="n">
         <v>4</v>
       </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3224,6 +4686,12 @@
       <c r="D201" t="n">
         <v>4</v>
       </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3238,6 +4706,12 @@
       <c r="D202" t="n">
         <v>4</v>
       </c>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>默认:压力预备,仅走 tier 基础难度</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3252,6 +4726,16 @@
       <c r="D203" t="n">
         <v>4</v>
       </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3266,6 +4750,12 @@
       <c r="D204" t="n">
         <v>4</v>
       </c>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3280,6 +4770,12 @@
       <c r="D205" t="n">
         <v>4</v>
       </c>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3294,6 +4790,16 @@
       <c r="D206" t="n">
         <v>4</v>
       </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3308,6 +4814,12 @@
       <c r="D207" t="n">
         <v>4</v>
       </c>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>默认:轮末前呼吸位</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3324,7 +4836,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>set_piece, hard_plus</t>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>大段 Boss:阶段能力检验</t>
         </is>
       </c>
     </row>
@@ -3341,6 +4858,16 @@
       <c r="D209" t="n">
         <v>5</v>
       </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3355,6 +4882,16 @@
       <c r="D210" t="n">
         <v>5</v>
       </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3369,6 +4906,12 @@
       <c r="D211" t="n">
         <v>5</v>
       </c>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3383,6 +4926,16 @@
       <c r="D212" t="n">
         <v>5</v>
       </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3397,6 +4950,16 @@
       <c r="D213" t="n">
         <v>5</v>
       </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3411,6 +4974,16 @@
       <c r="D214" t="n">
         <v>5</v>
       </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3425,6 +4998,12 @@
       <c r="D215" t="n">
         <v>5</v>
       </c>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3439,6 +5018,16 @@
       <c r="D216" t="n">
         <v>5</v>
       </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3453,6 +5042,16 @@
       <c r="D217" t="n">
         <v>5</v>
       </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3467,6 +5066,16 @@
       <c r="D218" t="n">
         <v>5</v>
       </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3481,6 +5090,16 @@
       <c r="D219" t="n">
         <v>5</v>
       </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3495,6 +5114,16 @@
       <c r="D220" t="n">
         <v>5</v>
       </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3509,6 +5138,12 @@
       <c r="D221" t="n">
         <v>5</v>
       </c>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3523,6 +5158,16 @@
       <c r="D222" t="n">
         <v>5</v>
       </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3537,6 +5182,16 @@
       <c r="D223" t="n">
         <v>5</v>
       </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -3551,6 +5206,12 @@
       <c r="D224" t="n">
         <v>5</v>
       </c>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -3565,6 +5226,12 @@
       <c r="D225" t="n">
         <v>5</v>
       </c>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -3579,6 +5246,16 @@
       <c r="D226" t="n">
         <v>5</v>
       </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -3593,6 +5270,16 @@
       <c r="D227" t="n">
         <v>5</v>
       </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -3607,6 +5294,16 @@
       <c r="D228" t="n">
         <v>5</v>
       </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -3621,6 +5318,16 @@
       <c r="D229" t="n">
         <v>5</v>
       </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -3635,6 +5342,16 @@
       <c r="D230" t="n">
         <v>5</v>
       </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -3649,6 +5366,12 @@
       <c r="D231" t="n">
         <v>5</v>
       </c>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -3663,6 +5386,16 @@
       <c r="D232" t="n">
         <v>5</v>
       </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -3677,6 +5410,16 @@
       <c r="D233" t="n">
         <v>5</v>
       </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -3691,6 +5434,16 @@
       <c r="D234" t="n">
         <v>5</v>
       </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -3705,6 +5458,12 @@
       <c r="D235" t="n">
         <v>5</v>
       </c>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -3719,6 +5478,16 @@
       <c r="D236" t="n">
         <v>5</v>
       </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -3733,6 +5502,16 @@
       <c r="D237" t="n">
         <v>5</v>
       </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -3747,6 +5526,16 @@
       <c r="D238" t="n">
         <v>5</v>
       </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -3761,6 +5550,16 @@
       <c r="D239" t="n">
         <v>5</v>
       </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -3775,6 +5574,16 @@
       <c r="D240" t="n">
         <v>5</v>
       </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -3789,6 +5598,12 @@
       <c r="D241" t="n">
         <v>5</v>
       </c>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -3803,6 +5618,16 @@
       <c r="D242" t="n">
         <v>5</v>
       </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -3817,6 +5642,16 @@
       <c r="D243" t="n">
         <v>5</v>
       </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -3831,6 +5666,12 @@
       <c r="D244" t="n">
         <v>5</v>
       </c>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -3845,6 +5686,12 @@
       <c r="D245" t="n">
         <v>5</v>
       </c>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -3859,6 +5706,16 @@
       <c r="D246" t="n">
         <v>5</v>
       </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -3873,6 +5730,16 @@
       <c r="D247" t="n">
         <v>5</v>
       </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -3887,6 +5754,16 @@
       <c r="D248" t="n">
         <v>5</v>
       </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -3901,6 +5778,16 @@
       <c r="D249" t="n">
         <v>5</v>
       </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -3915,6 +5802,16 @@
       <c r="D250" t="n">
         <v>5</v>
       </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -3929,6 +5826,12 @@
       <c r="D251" t="n">
         <v>5</v>
       </c>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -3943,6 +5846,16 @@
       <c r="D252" t="n">
         <v>5</v>
       </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -3957,6 +5870,16 @@
       <c r="D253" t="n">
         <v>5</v>
       </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -3971,6 +5894,16 @@
       <c r="D254" t="n">
         <v>5</v>
       </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -3985,6 +5918,12 @@
       <c r="D255" t="n">
         <v>5</v>
       </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>默认:复合预备,不额外抬压</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -3999,6 +5938,16 @@
       <c r="D256" t="n">
         <v>5</v>
       </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -4013,6 +5962,16 @@
       <c r="D257" t="n">
         <v>5</v>
       </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -4029,7 +5988,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>extreme_keeper</t>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>大段 Boss:阶段能力检验</t>
         </is>
       </c>
     </row>
@@ -4046,6 +6010,16 @@
       <c r="D259" t="n">
         <v>6</v>
       </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -4060,6 +6034,16 @@
       <c r="D260" t="n">
         <v>6</v>
       </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -4074,6 +6058,16 @@
       <c r="D261" t="n">
         <v>6</v>
       </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -4088,6 +6082,16 @@
       <c r="D262" t="n">
         <v>6</v>
       </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -4102,6 +6106,16 @@
       <c r="D263" t="n">
         <v>6</v>
       </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -4116,6 +6130,12 @@
       <c r="D264" t="n">
         <v>6</v>
       </c>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -4130,6 +6150,16 @@
       <c r="D265" t="n">
         <v>6</v>
       </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -4144,6 +6174,16 @@
       <c r="D266" t="n">
         <v>6</v>
       </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -4158,6 +6198,16 @@
       <c r="D267" t="n">
         <v>6</v>
       </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -4172,6 +6222,16 @@
       <c r="D268" t="n">
         <v>6</v>
       </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -4186,6 +6246,16 @@
       <c r="D269" t="n">
         <v>6</v>
       </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -4200,6 +6270,16 @@
       <c r="D270" t="n">
         <v>6</v>
       </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -4214,6 +6294,12 @@
       <c r="D271" t="n">
         <v>6</v>
       </c>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -4228,6 +6314,16 @@
       <c r="D272" t="n">
         <v>6</v>
       </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -4242,6 +6338,16 @@
       <c r="D273" t="n">
         <v>6</v>
       </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -4256,6 +6362,16 @@
       <c r="D274" t="n">
         <v>6</v>
       </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4270,6 +6386,16 @@
       <c r="D275" t="n">
         <v>6</v>
       </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4284,6 +6410,16 @@
       <c r="D276" t="n">
         <v>6</v>
       </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4298,6 +6434,16 @@
       <c r="D277" t="n">
         <v>6</v>
       </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4312,6 +6458,16 @@
       <c r="D278" t="n">
         <v>6</v>
       </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4326,6 +6482,16 @@
       <c r="D279" t="n">
         <v>6</v>
       </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4340,6 +6506,16 @@
       <c r="D280" t="n">
         <v>6</v>
       </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4354,6 +6530,16 @@
       <c r="D281" t="n">
         <v>6</v>
       </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4368,6 +6554,16 @@
       <c r="D282" t="n">
         <v>6</v>
       </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4382,6 +6578,16 @@
       <c r="D283" t="n">
         <v>6</v>
       </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -4396,6 +6602,12 @@
       <c r="D284" t="n">
         <v>6</v>
       </c>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4410,6 +6622,16 @@
       <c r="D285" t="n">
         <v>6</v>
       </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -4424,6 +6646,16 @@
       <c r="D286" t="n">
         <v>6</v>
       </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -4438,6 +6670,16 @@
       <c r="D287" t="n">
         <v>6</v>
       </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -4452,6 +6694,16 @@
       <c r="D288" t="n">
         <v>6</v>
       </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -4466,6 +6718,16 @@
       <c r="D289" t="n">
         <v>6</v>
       </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -4480,6 +6742,16 @@
       <c r="D290" t="n">
         <v>6</v>
       </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -4494,6 +6766,12 @@
       <c r="D291" t="n">
         <v>6</v>
       </c>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -4508,6 +6786,16 @@
       <c r="D292" t="n">
         <v>6</v>
       </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -4522,6 +6810,16 @@
       <c r="D293" t="n">
         <v>6</v>
       </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -4536,6 +6834,16 @@
       <c r="D294" t="n">
         <v>6</v>
       </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -4550,6 +6858,16 @@
       <c r="D295" t="n">
         <v>6</v>
       </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -4564,6 +6882,16 @@
       <c r="D296" t="n">
         <v>6</v>
       </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -4578,6 +6906,16 @@
       <c r="D297" t="n">
         <v>6</v>
       </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -4592,6 +6930,16 @@
       <c r="D298" t="n">
         <v>6</v>
       </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>轮末检验:提高一档难度</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -4606,6 +6954,16 @@
       <c r="D299" t="n">
         <v>6</v>
       </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -4620,6 +6978,16 @@
       <c r="D300" t="n">
         <v>6</v>
       </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -4634,6 +7002,16 @@
       <c r="D301" t="n">
         <v>6</v>
       </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -4648,6 +7026,16 @@
       <c r="D302" t="n">
         <v>6</v>
       </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -4662,6 +7050,16 @@
       <c r="D303" t="n">
         <v>6</v>
       </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -4676,6 +7074,12 @@
       <c r="D304" t="n">
         <v>6</v>
       </c>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -4690,6 +7094,16 @@
       <c r="D305" t="n">
         <v>6</v>
       </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -4704,6 +7118,16 @@
       <c r="D306" t="n">
         <v>6</v>
       </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>gk_test</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>难点:守门读秒与方向判断</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -4718,6 +7142,16 @@
       <c r="D307" t="n">
         <v>6</v>
       </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -4734,7 +7168,12 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>must_win</t>
+          <t>long_match, boss</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>大段 Boss:长局全胜检验</t>
         </is>
       </c>
     </row>
@@ -4751,6 +7190,16 @@
       <c r="D309" t="n">
         <v>7</v>
       </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -4765,6 +7214,16 @@
       <c r="D310" t="n">
         <v>7</v>
       </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -4779,6 +7238,12 @@
       <c r="D311" t="n">
         <v>7</v>
       </c>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -4793,6 +7258,16 @@
       <c r="D312" t="n">
         <v>7</v>
       </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -4807,6 +7282,16 @@
       <c r="D313" t="n">
         <v>7</v>
       </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -4821,6 +7306,16 @@
       <c r="D314" t="n">
         <v>7</v>
       </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -4835,6 +7330,16 @@
       <c r="D315" t="n">
         <v>7</v>
       </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -4849,6 +7354,16 @@
       <c r="D316" t="n">
         <v>7</v>
       </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -4863,6 +7378,16 @@
       <c r="D317" t="n">
         <v>7</v>
       </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -4877,6 +7402,16 @@
       <c r="D318" t="n">
         <v>7</v>
       </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -4891,6 +7426,16 @@
       <c r="D319" t="n">
         <v>7</v>
       </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -4905,6 +7450,16 @@
       <c r="D320" t="n">
         <v>7</v>
       </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -4919,6 +7474,16 @@
       <c r="D321" t="n">
         <v>7</v>
       </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -4933,6 +7498,16 @@
       <c r="D322" t="n">
         <v>7</v>
       </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -4947,6 +7522,16 @@
       <c r="D323" t="n">
         <v>7</v>
       </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -4961,6 +7546,12 @@
       <c r="D324" t="n">
         <v>7</v>
       </c>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -4975,6 +7566,16 @@
       <c r="D325" t="n">
         <v>7</v>
       </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -4989,6 +7590,16 @@
       <c r="D326" t="n">
         <v>7</v>
       </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -5003,6 +7614,16 @@
       <c r="D327" t="n">
         <v>7</v>
       </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -5017,6 +7638,16 @@
       <c r="D328" t="n">
         <v>7</v>
       </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -5031,6 +7662,16 @@
       <c r="D329" t="n">
         <v>7</v>
       </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -5045,6 +7686,16 @@
       <c r="D330" t="n">
         <v>7</v>
       </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -5059,6 +7710,12 @@
       <c r="D331" t="n">
         <v>7</v>
       </c>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -5073,6 +7730,16 @@
       <c r="D332" t="n">
         <v>7</v>
       </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -5087,6 +7754,16 @@
       <c r="D333" t="n">
         <v>7</v>
       </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -5101,6 +7778,16 @@
       <c r="D334" t="n">
         <v>7</v>
       </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -5115,6 +7802,16 @@
       <c r="D335" t="n">
         <v>7</v>
       </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -5129,6 +7826,16 @@
       <c r="D336" t="n">
         <v>7</v>
       </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -5143,6 +7850,16 @@
       <c r="D337" t="n">
         <v>7</v>
       </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -5157,6 +7874,16 @@
       <c r="D338" t="n">
         <v>7</v>
       </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -5171,6 +7898,16 @@
       <c r="D339" t="n">
         <v>7</v>
       </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -5185,6 +7922,16 @@
       <c r="D340" t="n">
         <v>7</v>
       </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -5199,6 +7946,16 @@
       <c r="D341" t="n">
         <v>7</v>
       </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -5213,6 +7970,16 @@
       <c r="D342" t="n">
         <v>7</v>
       </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -5227,6 +7994,16 @@
       <c r="D343" t="n">
         <v>7</v>
       </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -5241,6 +8018,12 @@
       <c r="D344" t="n">
         <v>7</v>
       </c>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -5255,6 +8038,16 @@
       <c r="D345" t="n">
         <v>7</v>
       </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -5269,6 +8062,16 @@
       <c r="D346" t="n">
         <v>7</v>
       </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -5283,6 +8086,16 @@
       <c r="D347" t="n">
         <v>7</v>
       </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -5297,6 +8110,16 @@
       <c r="D348" t="n">
         <v>7</v>
       </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -5311,6 +8134,16 @@
       <c r="D349" t="n">
         <v>7</v>
       </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -5325,6 +8158,16 @@
       <c r="D350" t="n">
         <v>7</v>
       </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -5339,6 +8182,12 @@
       <c r="D351" t="n">
         <v>7</v>
       </c>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -5353,6 +8202,16 @@
       <c r="D352" t="n">
         <v>7</v>
       </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -5367,6 +8226,16 @@
       <c r="D353" t="n">
         <v>7</v>
       </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -5381,6 +8250,16 @@
       <c r="D354" t="n">
         <v>7</v>
       </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -5395,6 +8274,16 @@
       <c r="D355" t="n">
         <v>7</v>
       </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -5409,6 +8298,16 @@
       <c r="D356" t="n">
         <v>7</v>
       </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -5423,6 +8322,16 @@
       <c r="D357" t="n">
         <v>7</v>
       </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>long_match, hard_plus</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>备战:长局叠加对手压力</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -5437,6 +8346,16 @@
       <c r="D358" t="n">
         <v>7</v>
       </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>long_match, boss</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>大段 Boss:长局全胜检验</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -5451,6 +8370,16 @@
       <c r="D359" t="n">
         <v>8</v>
       </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -5465,6 +8394,16 @@
       <c r="D360" t="n">
         <v>8</v>
       </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -5479,6 +8418,16 @@
       <c r="D361" t="n">
         <v>8</v>
       </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -5493,6 +8442,16 @@
       <c r="D362" t="n">
         <v>8</v>
       </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -5507,6 +8466,16 @@
       <c r="D363" t="n">
         <v>8</v>
       </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -5521,6 +8490,12 @@
       <c r="D364" t="n">
         <v>8</v>
       </c>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -5535,6 +8510,16 @@
       <c r="D365" t="n">
         <v>8</v>
       </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -5549,6 +8534,16 @@
       <c r="D366" t="n">
         <v>8</v>
       </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -5563,6 +8558,16 @@
       <c r="D367" t="n">
         <v>8</v>
       </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -5577,6 +8582,16 @@
       <c r="D368" t="n">
         <v>8</v>
       </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -5591,6 +8606,16 @@
       <c r="D369" t="n">
         <v>8</v>
       </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -5605,6 +8630,16 @@
       <c r="D370" t="n">
         <v>8</v>
       </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -5619,6 +8654,12 @@
       <c r="D371" t="n">
         <v>8</v>
       </c>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -5633,6 +8674,16 @@
       <c r="D372" t="n">
         <v>8</v>
       </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -5647,6 +8698,16 @@
       <c r="D373" t="n">
         <v>8</v>
       </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -5661,6 +8722,16 @@
       <c r="D374" t="n">
         <v>8</v>
       </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -5675,6 +8746,16 @@
       <c r="D375" t="n">
         <v>8</v>
       </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -5689,6 +8770,16 @@
       <c r="D376" t="n">
         <v>8</v>
       </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -5703,6 +8794,16 @@
       <c r="D377" t="n">
         <v>8</v>
       </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -5717,6 +8818,16 @@
       <c r="D378" t="n">
         <v>8</v>
       </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -5731,6 +8842,16 @@
       <c r="D379" t="n">
         <v>8</v>
       </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -5745,6 +8866,16 @@
       <c r="D380" t="n">
         <v>8</v>
       </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -5759,6 +8890,16 @@
       <c r="D381" t="n">
         <v>8</v>
       </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -5773,6 +8914,16 @@
       <c r="D382" t="n">
         <v>8</v>
       </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -5787,6 +8938,16 @@
       <c r="D383" t="n">
         <v>8</v>
       </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus, must_win</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -5801,6 +8962,12 @@
       <c r="D384" t="n">
         <v>8</v>
       </c>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -5815,6 +8982,16 @@
       <c r="D385" t="n">
         <v>8</v>
       </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -5829,6 +9006,16 @@
       <c r="D386" t="n">
         <v>8</v>
       </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -5843,6 +9030,16 @@
       <c r="D387" t="n">
         <v>8</v>
       </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -5857,6 +9054,16 @@
       <c r="D388" t="n">
         <v>8</v>
       </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -5871,6 +9078,16 @@
       <c r="D389" t="n">
         <v>8</v>
       </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -5885,6 +9102,16 @@
       <c r="D390" t="n">
         <v>8</v>
       </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -5899,6 +9126,12 @@
       <c r="D391" t="n">
         <v>8</v>
       </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -5913,6 +9146,16 @@
       <c r="D392" t="n">
         <v>8</v>
       </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -5927,6 +9170,16 @@
       <c r="D393" t="n">
         <v>8</v>
       </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -5941,6 +9194,16 @@
       <c r="D394" t="n">
         <v>8</v>
       </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -5955,6 +9218,16 @@
       <c r="D395" t="n">
         <v>8</v>
       </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -5969,6 +9242,16 @@
       <c r="D396" t="n">
         <v>8</v>
       </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -5983,6 +9266,16 @@
       <c r="D397" t="n">
         <v>8</v>
       </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -5997,6 +9290,16 @@
       <c r="D398" t="n">
         <v>8</v>
       </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -6011,6 +9314,16 @@
       <c r="D399" t="n">
         <v>8</v>
       </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -6025,6 +9338,16 @@
       <c r="D400" t="n">
         <v>8</v>
       </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -6039,6 +9362,16 @@
       <c r="D401" t="n">
         <v>8</v>
       </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -6053,6 +9386,16 @@
       <c r="D402" t="n">
         <v>8</v>
       </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -6067,6 +9410,16 @@
       <c r="D403" t="n">
         <v>8</v>
       </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -6081,6 +9434,12 @@
       <c r="D404" t="n">
         <v>8</v>
       </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -6095,6 +9454,16 @@
       <c r="D405" t="n">
         <v>8</v>
       </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -6109,6 +9478,16 @@
       <c r="D406" t="n">
         <v>8</v>
       </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -6123,6 +9502,16 @@
       <c r="D407" t="n">
         <v>8</v>
       </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -6139,7 +9528,12 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>tutorial</t>
+          <t>long_match, boss</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>大段 Boss:长局全胜检验</t>
         </is>
       </c>
     </row>
@@ -6156,6 +9550,16 @@
       <c r="D409" t="n">
         <v>9</v>
       </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -6170,6 +9574,16 @@
       <c r="D410" t="n">
         <v>9</v>
       </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -6184,6 +9598,12 @@
       <c r="D411" t="n">
         <v>9</v>
       </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -6198,6 +9618,16 @@
       <c r="D412" t="n">
         <v>9</v>
       </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -6212,6 +9642,16 @@
       <c r="D413" t="n">
         <v>9</v>
       </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -6226,6 +9666,16 @@
       <c r="D414" t="n">
         <v>9</v>
       </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -6240,6 +9690,16 @@
       <c r="D415" t="n">
         <v>9</v>
       </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -6254,6 +9714,16 @@
       <c r="D416" t="n">
         <v>9</v>
       </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -6268,6 +9738,16 @@
       <c r="D417" t="n">
         <v>9</v>
       </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -6282,6 +9762,16 @@
       <c r="D418" t="n">
         <v>9</v>
       </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -6296,6 +9786,16 @@
       <c r="D419" t="n">
         <v>9</v>
       </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -6310,6 +9810,16 @@
       <c r="D420" t="n">
         <v>9</v>
       </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -6324,6 +9834,16 @@
       <c r="D421" t="n">
         <v>9</v>
       </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -6338,6 +9858,16 @@
       <c r="D422" t="n">
         <v>9</v>
       </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -6352,6 +9882,16 @@
       <c r="D423" t="n">
         <v>9</v>
       </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -6366,6 +9906,12 @@
       <c r="D424" t="n">
         <v>9</v>
       </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -6380,6 +9926,16 @@
       <c r="D425" t="n">
         <v>9</v>
       </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -6394,6 +9950,16 @@
       <c r="D426" t="n">
         <v>9</v>
       </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -6408,6 +9974,16 @@
       <c r="D427" t="n">
         <v>9</v>
       </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -6422,6 +9998,16 @@
       <c r="D428" t="n">
         <v>9</v>
       </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>must_win, extreme_keeper</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -6436,6 +10022,16 @@
       <c r="D429" t="n">
         <v>9</v>
       </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -6450,6 +10046,16 @@
       <c r="D430" t="n">
         <v>9</v>
       </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -6464,6 +10070,12 @@
       <c r="D431" t="n">
         <v>9</v>
       </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -6478,6 +10090,16 @@
       <c r="D432" t="n">
         <v>9</v>
       </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -6492,6 +10114,16 @@
       <c r="D433" t="n">
         <v>9</v>
       </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus, must_win</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -6506,6 +10138,16 @@
       <c r="D434" t="n">
         <v>9</v>
       </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -6520,6 +10162,16 @@
       <c r="D435" t="n">
         <v>9</v>
       </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -6534,6 +10186,16 @@
       <c r="D436" t="n">
         <v>9</v>
       </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -6548,6 +10210,16 @@
       <c r="D437" t="n">
         <v>9</v>
       </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -6562,6 +10234,16 @@
       <c r="D438" t="n">
         <v>9</v>
       </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -6576,6 +10258,16 @@
       <c r="D439" t="n">
         <v>9</v>
       </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -6590,6 +10282,16 @@
       <c r="D440" t="n">
         <v>9</v>
       </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -6604,6 +10306,16 @@
       <c r="D441" t="n">
         <v>9</v>
       </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -6618,6 +10330,16 @@
       <c r="D442" t="n">
         <v>9</v>
       </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -6632,6 +10354,16 @@
       <c r="D443" t="n">
         <v>9</v>
       </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -6646,6 +10378,12 @@
       <c r="D444" t="n">
         <v>9</v>
       </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -6660,6 +10398,16 @@
       <c r="D445" t="n">
         <v>9</v>
       </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -6674,6 +10422,16 @@
       <c r="D446" t="n">
         <v>9</v>
       </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -6688,6 +10446,16 @@
       <c r="D447" t="n">
         <v>9</v>
       </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -6702,6 +10470,16 @@
       <c r="D448" t="n">
         <v>9</v>
       </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>must_win, extreme_keeper</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -6716,6 +10494,16 @@
       <c r="D449" t="n">
         <v>9</v>
       </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -6730,6 +10518,16 @@
       <c r="D450" t="n">
         <v>9</v>
       </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -6744,6 +10542,12 @@
       <c r="D451" t="n">
         <v>9</v>
       </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
@@ -6758,6 +10562,16 @@
       <c r="D452" t="n">
         <v>9</v>
       </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -6772,6 +10586,16 @@
       <c r="D453" t="n">
         <v>9</v>
       </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -6786,6 +10610,16 @@
       <c r="D454" t="n">
         <v>9</v>
       </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -6800,6 +10634,16 @@
       <c r="D455" t="n">
         <v>9</v>
       </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -6814,6 +10658,16 @@
       <c r="D456" t="n">
         <v>9</v>
       </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -6828,6 +10682,16 @@
       <c r="D457" t="n">
         <v>9</v>
       </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -6842,6 +10706,16 @@
       <c r="D458" t="n">
         <v>9</v>
       </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>long_match, extreme_keeper, boss</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>大段 Boss:终局长局+极限门将+全胜要求</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -6856,6 +10730,16 @@
       <c r="D459" t="n">
         <v>10</v>
       </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -6870,6 +10754,16 @@
       <c r="D460" t="n">
         <v>10</v>
       </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -6884,6 +10778,16 @@
       <c r="D461" t="n">
         <v>10</v>
       </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -6898,6 +10802,16 @@
       <c r="D462" t="n">
         <v>10</v>
       </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -6912,6 +10826,16 @@
       <c r="D463" t="n">
         <v>10</v>
       </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -6926,6 +10850,12 @@
       <c r="D464" t="n">
         <v>10</v>
       </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -6940,6 +10870,16 @@
       <c r="D465" t="n">
         <v>10</v>
       </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
@@ -6954,6 +10894,16 @@
       <c r="D466" t="n">
         <v>10</v>
       </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -6968,6 +10918,16 @@
       <c r="D467" t="n">
         <v>10</v>
       </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
@@ -6982,6 +10942,16 @@
       <c r="D468" t="n">
         <v>10</v>
       </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>must_win, extreme_keeper</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -6996,6 +10966,16 @@
       <c r="D469" t="n">
         <v>10</v>
       </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -7010,6 +10990,16 @@
       <c r="D470" t="n">
         <v>10</v>
       </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -7024,6 +11014,12 @@
       <c r="D471" t="n">
         <v>10</v>
       </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -7038,6 +11034,16 @@
       <c r="D472" t="n">
         <v>10</v>
       </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -7052,6 +11058,16 @@
       <c r="D473" t="n">
         <v>10</v>
       </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -7066,6 +11082,16 @@
       <c r="D474" t="n">
         <v>10</v>
       </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -7080,6 +11106,16 @@
       <c r="D475" t="n">
         <v>10</v>
       </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -7094,6 +11130,16 @@
       <c r="D476" t="n">
         <v>10</v>
       </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -7108,6 +11154,16 @@
       <c r="D477" t="n">
         <v>10</v>
       </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -7122,6 +11178,16 @@
       <c r="D478" t="n">
         <v>10</v>
       </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -7136,6 +11202,16 @@
       <c r="D479" t="n">
         <v>10</v>
       </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -7150,6 +11226,16 @@
       <c r="D480" t="n">
         <v>10</v>
       </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -7164,6 +11250,16 @@
       <c r="D481" t="n">
         <v>10</v>
       </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -7178,6 +11274,16 @@
       <c r="D482" t="n">
         <v>10</v>
       </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -7192,6 +11298,16 @@
       <c r="D483" t="n">
         <v>10</v>
       </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus, must_win</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -7206,6 +11322,12 @@
       <c r="D484" t="n">
         <v>10</v>
       </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -7220,6 +11342,16 @@
       <c r="D485" t="n">
         <v>10</v>
       </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -7234,6 +11366,16 @@
       <c r="D486" t="n">
         <v>10</v>
       </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -7248,6 +11390,16 @@
       <c r="D487" t="n">
         <v>10</v>
       </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -7262,6 +11414,16 @@
       <c r="D488" t="n">
         <v>10</v>
       </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>must_win, extreme_keeper</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -7276,6 +11438,16 @@
       <c r="D489" t="n">
         <v>10</v>
       </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -7290,6 +11462,16 @@
       <c r="D490" t="n">
         <v>10</v>
       </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -7304,6 +11486,12 @@
       <c r="D491" t="n">
         <v>10</v>
       </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>默认:保留基础节奏,让玩家消化前一关技巧</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -7318,6 +11506,16 @@
       <c r="D492" t="n">
         <v>10</v>
       </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -7332,6 +11530,16 @@
       <c r="D493" t="n">
         <v>10</v>
       </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -7346,6 +11554,16 @@
       <c r="D494" t="n">
         <v>10</v>
       </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>恢复:缩短局长并降低 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -7360,6 +11578,16 @@
       <c r="D495" t="n">
         <v>10</v>
       </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -7374,6 +11602,16 @@
       <c r="D496" t="n">
         <v>10</v>
       </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -7388,6 +11626,16 @@
       <c r="D497" t="n">
         <v>10</v>
       </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -7402,6 +11650,16 @@
       <c r="D498" t="n">
         <v>10</v>
       </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>must_win</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>轮末检验:无平局空间</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -7416,6 +11674,16 @@
       <c r="D499" t="n">
         <v>10</v>
       </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>short_match, easy_minus</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>恢复:降低一档压力,避免连续挫败</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -7430,6 +11698,16 @@
       <c r="D500" t="n">
         <v>10</v>
       </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>set_piece</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>技巧主题:任意球/点球基础复习</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -7444,6 +11722,16 @@
       <c r="D501" t="n">
         <v>10</v>
       </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>corner_focus</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>变化:角球变化,打破单一射门</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -7458,6 +11746,16 @@
       <c r="D502" t="n">
         <v>10</v>
       </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>hard_plus</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>压力:提高 AI 与对手星级,制造专注点</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -7472,6 +11770,16 @@
       <c r="D503" t="n">
         <v>10</v>
       </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>set_piece, hard_plus</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>小高潮:定位球复合考验</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -7486,6 +11794,12 @@
       <c r="D504" t="n">
         <v>10</v>
       </c>
+      <c r="E504" t="inlineStr"/>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>默认恢复:不额外改写,降低 tag 密度</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -7500,6 +11814,16 @@
       <c r="D505" t="n">
         <v>10</v>
       </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>all_v2</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>复合:全 v2 切片,提升操作变化</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -7514,6 +11838,16 @@
       <c r="D506" t="n">
         <v>10</v>
       </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>gk_test, hard_plus</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>难点:守门考验叠加 AI 压力</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -7528,6 +11862,16 @@
       <c r="D507" t="n">
         <v>10</v>
       </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>long_match, narrow_angle</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>备战:长局叠加收窄角度</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -7541,6 +11885,16 @@
       </c>
       <c r="D508" t="n">
         <v>10</v>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>long_match, extreme_keeper, boss</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>大段 Boss:终局长局+极限门将+全胜要求</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -7623,11 +11977,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>

--- a/output/test-config/level-tags/LevelTagCfg.xlsx
+++ b/output/test-config/level-tags/LevelTagCfg.xlsx
@@ -513,6 +513,11 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="n">
         <v>1</v>
@@ -528,12 +533,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>tutorial, free_run</t>
+          <t>tutorial, penalty_focus</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -740,12 +745,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -948,12 +953,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1165,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -1368,12 +1373,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -1584,12 +1589,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -1796,12 +1801,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -2012,12 +2017,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -2224,12 +2229,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2445,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>short_match, free_run</t>
+          <t>short_match, penalty_focus</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>恢复:短局免票,给玩家重新进入心流</t>
+          <t>恢复:短局点球确定性,给玩家重新进入心流</t>
         </is>
       </c>
     </row>
@@ -11977,6 +11982,11 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -12075,129 +12085,134 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>free_run</t>
+          <t>gk_test</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>slice</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>门票消耗 0</t>
+          <t>末位强制 goalkeep v2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gk_test</t>
+          <t>hard_plus</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>slice</t>
+          <t>ai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>difficulty</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>末位强制 goalkeep v2</t>
+          <t>AiProfile +1 + OpponentStar +1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>hard_plus</t>
+          <t>lenient</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ai</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>difficulty</t>
+          <t>threshold</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AiProfile +1 + OpponentStar +1</t>
+          <t>胜阈值降至 40%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>lenient</t>
+          <t>long_match</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>slice</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>threshold</t>
+          <t>length</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>胜阈值降至 40%</t>
+          <t>切片数 +1(上限 5)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>long_match</t>
+          <t>must_win</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>slice</t>
+          <t>level</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>length</t>
+          <t>threshold</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>切片数 +1(上限 5)</t>
+          <t>切片全胜才能赢</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>must_win</t>
+          <t>narrow_angle</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>ai</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>threshold</t>
+          <t>modifier</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>切片全胜才能赢</t>
+          <t>ModifierID 强制 4006</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>narrow_angle</t>
+          <t>no_modifier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -12212,29 +12227,24 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ModifierID 强制 4006</t>
+          <t>ModifierID 强制 0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>no_modifier</t>
+          <t>penalty_focus</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ai</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>modifier</t>
+          <t>slice</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ModifierID 强制 0</t>
+          <t>保证至少 1 penalty 切片</t>
         </is>
       </c>
     </row>
